--- a/src/attributions/attributions_saliency_traj_186.xlsx
+++ b/src/attributions/attributions_saliency_traj_186.xlsx
@@ -1568,571 +1568,571 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.04633080586791039</v>
+        <v>0.2399097830057144</v>
       </c>
       <c r="B3" t="n">
-        <v>1.398853063583374</v>
+        <v>1.013849973678589</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1109821572899818</v>
+        <v>0.03761079162359238</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1575957834720612</v>
+        <v>0.1836898475885391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2564308047294617</v>
+        <v>0.2927322387695312</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9568383693695068</v>
+        <v>0.9895703792572021</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08252859115600586</v>
+        <v>0.1690250337123871</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3500640690326691</v>
+        <v>0.157779723405838</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07315648347139359</v>
+        <v>0.09867028892040253</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2915394306182861</v>
+        <v>0.07388637959957123</v>
       </c>
       <c r="K3" t="n">
-        <v>1.103485345840454</v>
+        <v>1.039882898330688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.078619584441185</v>
+        <v>0.06164567917585373</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4576326012611389</v>
+        <v>0.1307522654533386</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1384726464748383</v>
+        <v>0.1754396855831146</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8585432767868042</v>
+        <v>0.7977789044380188</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1067861020565033</v>
+        <v>0.1176356226205826</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.169792577624321</v>
+        <v>0.1562759578227997</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03863321989774704</v>
+        <v>0.08436205238103867</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09754790365695953</v>
+        <v>0.1318510472774506</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1591660231351852</v>
+        <v>0.2129693478345871</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06853651255369186</v>
+        <v>0.3514400720596313</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01677083782851696</v>
+        <v>0.1957961618900299</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04250691086053848</v>
+        <v>0.1623892039060593</v>
       </c>
       <c r="X3" t="n">
-        <v>0.003396846354007721</v>
+        <v>0.1232104450464249</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02403359115123749</v>
+        <v>0.4611946642398834</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05737371370196342</v>
+        <v>0.2256110310554504</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06083428114652634</v>
+        <v>0.1278435438871384</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1014819517731667</v>
+        <v>0.2884005904197693</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1546392142772675</v>
+        <v>0.1974932998418808</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.06281271576881409</v>
+        <v>0.08210349082946777</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05137146636843681</v>
+        <v>0.584425687789917</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1809680908918381</v>
+        <v>0.05340040102601051</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.08192146569490433</v>
+        <v>0.2839564383029938</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.05886268615722656</v>
+        <v>0.2065864056348801</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.009941617958247662</v>
+        <v>0.3234385251998901</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.01149642933160067</v>
+        <v>0.2309797555208206</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.004101892933249474</v>
+        <v>0.05632561445236206</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1284663826227188</v>
+        <v>0.0975092425942421</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.02752580307424068</v>
+        <v>0.0167900025844574</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.01438598334789276</v>
+        <v>0.1256619691848755</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1003113612532616</v>
+        <v>0.1454288065433502</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.2247029542922974</v>
+        <v>0.2058137804269791</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0120712835341692</v>
+        <v>0.3022844195365906</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.005271376576274633</v>
+        <v>0.1407855749130249</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1251956969499588</v>
+        <v>0.05958401411771774</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.139881044626236</v>
+        <v>0.06344048678874969</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.7461894750595093</v>
+        <v>0.5153886675834656</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.03424012660980225</v>
+        <v>0.215164989233017</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.06396220624446869</v>
+        <v>0.1331683993339539</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1282406449317932</v>
+        <v>0.5208607912063599</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.6292080879211426</v>
+        <v>0.5401260256767273</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.0963878259062767</v>
+        <v>0.2140494883060455</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0001548189902678132</v>
+        <v>0.09727467596530914</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1536636352539062</v>
+        <v>0.1563924551010132</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.07330451160669327</v>
+        <v>0.1423075646162033</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.3589407205581665</v>
+        <v>0.6358727812767029</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.1512521356344223</v>
+        <v>0.1050949469208717</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1803587824106216</v>
+        <v>0.3762604892253876</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.1099517196416855</v>
+        <v>0.480891227722168</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.2341777682304382</v>
+        <v>0.3263684511184692</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1650353074073792</v>
+        <v>0.04744116961956024</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01843613758683205</v>
+        <v>0.244661808013916</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.1420170664787292</v>
+        <v>0.1051215752959251</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02114243246614933</v>
+        <v>0.09439675509929657</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.06988542526960373</v>
+        <v>0.07095527648925781</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.03624380752444267</v>
+        <v>0.05201742053031921</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.08422853797674179</v>
+        <v>0.001979410648345947</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.07006809860467911</v>
+        <v>0.07563988119363785</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.02764030173420906</v>
+        <v>0.1871307939291</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.009051050990819931</v>
+        <v>0.06482656300067902</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.03248778358101845</v>
+        <v>0.06572806835174561</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.02355365082621574</v>
+        <v>0.1156130358576775</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1090420335531235</v>
+        <v>0.05694875121116638</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.3342616558074951</v>
+        <v>0.2210309207439423</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1310519576072693</v>
+        <v>0.2619659304618835</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.01721895299851894</v>
+        <v>0.1224787458777428</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1826077103614807</v>
+        <v>0.1506724059581757</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2542281448841095</v>
+        <v>0.4202522039413452</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.1215759217739105</v>
+        <v>0.5047359466552734</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.1579393595457077</v>
+        <v>0.04084669053554535</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.009530495852231979</v>
+        <v>0.0182475745677948</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.012780936434865</v>
+        <v>0.05417748168110847</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.2649079859256744</v>
+        <v>0.2802380621433258</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0562547855079174</v>
+        <v>0.04677186906337738</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.03512372076511383</v>
+        <v>0.09333262592554092</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01265935227274895</v>
+        <v>0.07426296174526215</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1555144488811493</v>
+        <v>0.2094000726938248</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.004735395312309265</v>
+        <v>0.02316963858902454</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.03839389234781265</v>
+        <v>0.03496584296226501</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.002034023404121399</v>
+        <v>0.01578664593398571</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1447746902704239</v>
+        <v>0.3132940530776978</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01171972882002592</v>
+        <v>0.5436065793037415</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0196115355938673</v>
+        <v>0.3877679705619812</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.006694244220852852</v>
+        <v>0.2517918348312378</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.02587321773171425</v>
+        <v>0.03604229912161827</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.03160351887345314</v>
+        <v>0.222325786948204</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.04262559860944748</v>
+        <v>0.006315246690064669</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1112372875213623</v>
+        <v>0.1713114082813263</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.09578883647918701</v>
+        <v>0.2202626615762711</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01226914208382368</v>
+        <v>0.03927475586533546</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.2253971099853516</v>
+        <v>0.260709285736084</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.06582463532686234</v>
+        <v>0.0116922315210104</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.07489421963691711</v>
+        <v>0.05070685595273972</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01441285386681557</v>
+        <v>0.05062972754240036</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.1697355806827545</v>
+        <v>0.1846622675657272</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0278853140771389</v>
+        <v>0.03161366656422615</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0427548959851265</v>
+        <v>0.00563731649890542</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.007063203491270542</v>
+        <v>0.01519102789461613</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08728198707103729</v>
+        <v>0.41147780418396</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.06252773106098175</v>
+        <v>0.2085175663232803</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1500358581542969</v>
+        <v>0.3211541175842285</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1309079676866531</v>
+        <v>0.1344718039035797</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.212610125541687</v>
+        <v>0.2051892429590225</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1466327905654907</v>
+        <v>0.7192248702049255</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.01109365373849869</v>
+        <v>0.1847102046012878</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.3219499886035919</v>
+        <v>0.2119549661874771</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.1683781743049622</v>
+        <v>0.2283026278018951</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.01398432347923517</v>
+        <v>0.03543742746114731</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.05035220459103584</v>
+        <v>0.2246249318122864</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.1292447596788406</v>
+        <v>0.1286417245864868</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.05682580545544624</v>
+        <v>0.3082333207130432</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.06671135872602463</v>
+        <v>0.06908723711967468</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.04201072454452515</v>
+        <v>0.06274472177028656</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.06978278607130051</v>
+        <v>0.06065261736512184</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1021595969796181</v>
+        <v>0.09133797883987427</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.03496072441339493</v>
+        <v>0.07223081588745117</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.03365123271942139</v>
+        <v>0.1521478742361069</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.151173010468483</v>
+        <v>0.192652702331543</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.03952560573816299</v>
+        <v>0.002948835492134094</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0394047275185585</v>
+        <v>0.02574952691793442</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.06994099915027618</v>
+        <v>0.1816238760948181</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.03660418093204498</v>
+        <v>0.353652685880661</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.04193311184644699</v>
+        <v>0.03415653854608536</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.07971393316984177</v>
+        <v>0.339955598115921</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.06062737107276917</v>
+        <v>0.3351921439170837</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.00430121086537838</v>
+        <v>0.09019927680492401</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.249579057097435</v>
+        <v>0.1083600670099258</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.02746265754103661</v>
+        <v>0.1362262368202209</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.08047179877758026</v>
+        <v>0.2322580367326736</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.01352311670780182</v>
+        <v>0.05508147925138474</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1620532125234604</v>
+        <v>0.2280784547328949</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.03141183033585548</v>
+        <v>0.1072989106178284</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.09860029816627502</v>
+        <v>0.09411206096410751</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02911192178726196</v>
+        <v>0.05548331514000893</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.06642324477434158</v>
+        <v>0.07875146716833115</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.1577625125646591</v>
+        <v>0.1729950159788132</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0762496218085289</v>
+        <v>0.2336075156927109</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.03941654413938522</v>
+        <v>0.2104649394750595</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.01784498244524002</v>
+        <v>0.3402835726737976</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.1566862612962723</v>
+        <v>0.2830723226070404</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.07597161084413528</v>
+        <v>0.04641042649745941</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.006022429093718529</v>
+        <v>0.1027007400989532</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.09844908118247986</v>
+        <v>0.03707390278577805</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.03386234492063522</v>
+        <v>0.05157460272312164</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.2404150366783142</v>
+        <v>0.2380893528461456</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.01548738218843937</v>
+        <v>0.01871387660503387</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01485441625118256</v>
+        <v>0.03355413675308228</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.002890393137931824</v>
+        <v>0.133186548948288</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.160024106502533</v>
+        <v>0.1861100643873215</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.006569409742951393</v>
+        <v>0.01030563563108444</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.02785877510905266</v>
+        <v>0.02563351206481457</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.006970783695578575</v>
+        <v>0.03056104108691216</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.0532214343547821</v>
+        <v>0.2331602424383163</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.06381963193416595</v>
+        <v>0.03016394749283791</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.02866150811314583</v>
+        <v>0.2102744579315186</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1937187612056732</v>
+        <v>0.03535535559058189</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1326478570699692</v>
+        <v>0.1633219420909882</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1781927943229675</v>
+        <v>0.3878432810306549</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.08148021250963211</v>
+        <v>0.1530358791351318</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.04552333056926727</v>
+        <v>0.1445317268371582</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.1512444317340851</v>
+        <v>0.4289631545543671</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1118333041667938</v>
+        <v>0.4351146519184113</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.4739928841590881</v>
+        <v>0.2350162863731384</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0244906023144722</v>
+        <v>0.1674621552228928</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.225468784570694</v>
+        <v>0.08358579874038696</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.007776199840009212</v>
+        <v>0.01781926490366459</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.2064915001392365</v>
+        <v>0.1091908365488052</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.1254486590623856</v>
+        <v>0.08181271702051163</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.06267836689949036</v>
+        <v>0.1037713438272476</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.05156383290886879</v>
+        <v>0.1130975261330605</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.1596779972314835</v>
+        <v>0.2935602068901062</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.1167466044425964</v>
+        <v>0.09033163636922836</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.032353475689888</v>
+        <v>0.07272975146770477</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.03329040110111237</v>
+        <v>0.09208226203918457</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.4435235559940338</v>
+        <v>0.4464950263500214</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1374753564596176</v>
+        <v>0.2792279124259949</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.008656424470245838</v>
+        <v>0.1458830088376999</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.09977608919143677</v>
+        <v>0.1661376804113388</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.005286445841193199</v>
+        <v>0.317223459482193</v>
       </c>
     </row>
     <row r="4">
@@ -2706,1140 +2706,1140 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0002206075878348202</v>
+        <v>0.02968575060367584</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001458041719160974</v>
+        <v>0.1365064680576324</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0002225774951511994</v>
+        <v>0.03252001106739044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0004422489437274635</v>
+        <v>0.00282061193138361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0004269056371413171</v>
+        <v>0.01097536273300648</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000867034774273634</v>
+        <v>0.1433321833610535</v>
       </c>
       <c r="G5" t="n">
-        <v>4.831291153095663e-05</v>
+        <v>0.02043364197015762</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002166553022107109</v>
+        <v>0.04322174191474915</v>
       </c>
       <c r="I5" t="n">
-        <v>3.304089477751404e-05</v>
+        <v>0.01751092076301575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000216492626350373</v>
+        <v>0.003534094430506229</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001349495491012931</v>
+        <v>0.162143349647522</v>
       </c>
       <c r="L5" t="n">
-        <v>8.484009595122188e-05</v>
+        <v>0.04395407438278198</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0008404514519497752</v>
+        <v>0.03954212740063667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0004723800229839981</v>
+        <v>0.06481015682220459</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001012155786156654</v>
+        <v>0.1542423069477081</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0002581601729616523</v>
+        <v>0.004464489873498678</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0001581347751198336</v>
+        <v>0.0001326780766248703</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0002033455675700679</v>
+        <v>0.02038099244236946</v>
       </c>
       <c r="S5" t="n">
-        <v>6.171814311528578e-05</v>
+        <v>0.00350492331199348</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0002702576166484505</v>
+        <v>0.02759794145822525</v>
       </c>
       <c r="U5" t="n">
-        <v>7.816031939000823e-06</v>
+        <v>0.02189682237803936</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0001551146560814232</v>
+        <v>0.04529817774891853</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0002893978962674737</v>
+        <v>0.03709165751934052</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0001065542746800929</v>
+        <v>0.01790796965360641</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.821018466027454e-05</v>
+        <v>0.003851410001516342</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0001330595696344972</v>
+        <v>0.01474982593208551</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001291725784540176</v>
+        <v>0.0102877551689744</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003278878284618258</v>
+        <v>0.00562808895483613</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0002439262316329405</v>
+        <v>0.02506617084145546</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002957767865154892</v>
+        <v>0.01217783987522125</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0002291274577146396</v>
+        <v>0.04576687514781952</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0002438378578517586</v>
+        <v>0.05322758108377457</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.569566514575854e-05</v>
+        <v>0.02801210805773735</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0002364681859035045</v>
+        <v>0.003453370183706284</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.36377847311087e-05</v>
+        <v>0.08133172988891602</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0001143729532486759</v>
+        <v>0.00170408608391881</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.540154673624784e-05</v>
+        <v>0.004601914435625076</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0003589345142245293</v>
+        <v>0.04065064340829849</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.468378367368132e-05</v>
+        <v>0.01787891238927841</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.049280010396615e-05</v>
+        <v>0.02548237331211567</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000133461260702461</v>
+        <v>0.01772403903305531</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.913167403079569e-05</v>
+        <v>0.01684181019663811</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.00012249342398718</v>
+        <v>0.009535512886941433</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.633374166791327e-05</v>
+        <v>0.03450479358434677</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.612143180158455e-05</v>
+        <v>0.02488207258284092</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0001147305010817945</v>
+        <v>0.003495043609291315</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.001018478069454432</v>
+        <v>0.1705766469240189</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0001706439506961033</v>
+        <v>0.02853532508015633</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.0002394622715655714</v>
+        <v>0.01356939412653446</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.981799298140686e-05</v>
+        <v>0.05511416494846344</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.431627945043147e-05</v>
+        <v>0.09453395754098892</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0004457334289327264</v>
+        <v>0.01915445551276207</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.000254972284892574</v>
+        <v>4.235364031046629e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.315464608836919e-05</v>
+        <v>0.01316860876977444</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.30272310343571e-05</v>
+        <v>0.01234642695635557</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0002670557587407529</v>
+        <v>0.02053525298833847</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0002597788407001644</v>
+        <v>0.02726794593036175</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.998474757187068e-06</v>
+        <v>0.001645047217607498</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.000556973391212523</v>
+        <v>0.01132243033498526</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0004903983208350837</v>
+        <v>0.001415372127667069</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0002477859379723668</v>
+        <v>0.01069800741970539</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3.76140778826084e-05</v>
+        <v>0.02425155602395535</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0002347004774492234</v>
+        <v>0.006099001970142126</v>
       </c>
       <c r="BL5" t="n">
-        <v>5.801412771688774e-05</v>
+        <v>0.01100324839353561</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0002367344277445227</v>
+        <v>0.02507113292813301</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.894588785944507e-05</v>
+        <v>0.004112665541470051</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0001120676170103252</v>
+        <v>0.02015190944075584</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0002425940911052749</v>
+        <v>0.01985873654484749</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.881267886958085e-05</v>
+        <v>0.02426251024007797</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0001316507114097476</v>
+        <v>0.05127719789743423</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.256958709447645e-05</v>
+        <v>0.0005711351986974478</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.010092667769641e-05</v>
+        <v>0.02577266842126846</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.130661106202751e-05</v>
+        <v>0.01482042204588652</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0005306008970364928</v>
+        <v>0.1040412336587906</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.115433203987777e-05</v>
+        <v>0.01730508171021938</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.0001367484801448882</v>
+        <v>0.05098235607147217</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.913383499020711e-05</v>
+        <v>0.02133786305785179</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.324293200217653e-05</v>
+        <v>0.05677987635135651</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0002380783844273537</v>
+        <v>0.0153519231826067</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.534960342221893e-06</v>
+        <v>0.003778367070481181</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.65931989310775e-05</v>
+        <v>0.01188309863209724</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.836241664132103e-05</v>
+        <v>0.006928506307303905</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0002391785237705335</v>
+        <v>0.04720205441117287</v>
       </c>
       <c r="CF5" t="n">
-        <v>1.062775936588878e-06</v>
+        <v>0.004775163717567921</v>
       </c>
       <c r="CG5" t="n">
-        <v>9.580911137163639e-05</v>
+        <v>0.01212853193283081</v>
       </c>
       <c r="CH5" t="n">
-        <v>4.904851812170818e-05</v>
+        <v>0.002154430840164423</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0001606149307917804</v>
+        <v>0.0326109305024147</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0001294365501962602</v>
+        <v>0.01268318761140108</v>
       </c>
       <c r="CK5" t="n">
-        <v>3.750815812963992e-05</v>
+        <v>0.01080561615526676</v>
       </c>
       <c r="CL5" t="n">
-        <v>4.179047027719207e-05</v>
+        <v>0.01013164408504963</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.000205997028388083</v>
+        <v>0.02926829643547535</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0001627617311896756</v>
+        <v>0.07387980073690414</v>
       </c>
       <c r="CO5" t="n">
-        <v>5.213105032453313e-05</v>
+        <v>0.03724948316812515</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.31067679123953e-06</v>
+        <v>0.0409446507692337</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0001260844292119145</v>
+        <v>0.02516608498990536</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0002901178377214819</v>
+        <v>0.003122415859252214</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0002491967170499265</v>
+        <v>0.02724909037351608</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0003845276369247586</v>
+        <v>0.004742736928164959</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0002219675225205719</v>
+        <v>0.001001189462840557</v>
       </c>
       <c r="CV5" t="n">
-        <v>5.921100455452688e-05</v>
+        <v>0.002162986434996128</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0002058946702163666</v>
+        <v>0.04088830202817917</v>
       </c>
       <c r="CX5" t="n">
-        <v>4.550995799945667e-05</v>
+        <v>0.007918364368379116</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0001016643655020744</v>
+        <v>0.006970414891839027</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.706030525383539e-05</v>
+        <v>0.0006713159382343292</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001762715837685391</v>
+        <v>0.03541545569896698</v>
       </c>
       <c r="DB5" t="n">
-        <v>7.671427738387138e-05</v>
+        <v>0.006801032461225986</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.332174360868521e-05</v>
+        <v>0.008431045338511467</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.109953493345529e-05</v>
+        <v>0.007849960587918758</v>
       </c>
       <c r="DE5" t="n">
-        <v>9.258476347895339e-05</v>
+        <v>0.0161544606089592</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.000260337081272155</v>
+        <v>0.02601867169141769</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0003704421105794609</v>
+        <v>0.01976818963885307</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0001619827817194164</v>
+        <v>0.003376955166459084</v>
       </c>
       <c r="DI5" t="n">
-        <v>1.211552444146946e-05</v>
+        <v>0.01433655992150307</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0003850498469546437</v>
+        <v>0.02485381439328194</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0002289187395945191</v>
+        <v>0.01163951493799686</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0001534690090920776</v>
+        <v>0.03706367686390877</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0002912035561166704</v>
+        <v>0.01768843829631805</v>
       </c>
       <c r="DN5" t="n">
-        <v>6.922854663571343e-05</v>
+        <v>0.007379839662462473</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0001614904031157494</v>
+        <v>0.01981324702501297</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001851744746090844</v>
+        <v>0.001646695658564568</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0003596328315325081</v>
+        <v>0.01879826746881008</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0002430248277960345</v>
+        <v>0.01022472698241472</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0003420467546675354</v>
+        <v>0.007531879004091024</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0001608179009053856</v>
+        <v>0.0006397725082933903</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.000142073942697607</v>
+        <v>0.0125091727823019</v>
       </c>
       <c r="DV5" t="n">
-        <v>4.140605960856192e-05</v>
+        <v>0.01492400001734495</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0001568274601595476</v>
+        <v>0.017807487398386</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.831093484535813e-05</v>
+        <v>0.01524186413735151</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.000151512780576013</v>
+        <v>0.02650105580687523</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0004381779581308365</v>
+        <v>0.01613531075417995</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0001012568245641887</v>
+        <v>0.008318194188177586</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0002179211005568504</v>
+        <v>0.02804387360811234</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0001329792139586061</v>
+        <v>0.001453407225199044</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0003364782896824181</v>
+        <v>0.007432925049215555</v>
       </c>
       <c r="EE5" t="n">
-        <v>8.075020741671324e-05</v>
+        <v>0.03596089780330658</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0001086003612726927</v>
+        <v>0.001153351273387671</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.000205786491278559</v>
+        <v>0.01016285456717014</v>
       </c>
       <c r="EH5" t="n">
-        <v>2.231908729299903e-05</v>
+        <v>0.006595231126993895</v>
       </c>
       <c r="EI5" t="n">
-        <v>4.414484646986239e-05</v>
+        <v>0.03245760500431061</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0001149551244452596</v>
+        <v>0.01962577365338802</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0001575190253788605</v>
+        <v>0.01579501293599606</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0001581963879289106</v>
+        <v>0.001433414174243808</v>
       </c>
       <c r="EM5" t="n">
-        <v>4.260008063283749e-05</v>
+        <v>0.003351267194375396</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.692054865998216e-05</v>
+        <v>0.009632113389670849</v>
       </c>
       <c r="EO5" t="n">
-        <v>3.559614560799673e-05</v>
+        <v>0.004441376775503159</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0001649047044338658</v>
+        <v>0.02868261560797691</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0001550035667605698</v>
+        <v>0.008403715677559376</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0001098212524084374</v>
+        <v>0.005959507077932358</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0003199728380423039</v>
+        <v>0.0253260899335146</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.0001331830280832946</v>
+        <v>0.009015068411827087</v>
       </c>
       <c r="EU5" t="n">
-        <v>1.135572529165074e-05</v>
+        <v>0.005786692723631859</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0002301178756169975</v>
+        <v>0.007668283767998219</v>
       </c>
       <c r="EW5" t="n">
-        <v>4.197219823254272e-05</v>
+        <v>0.0002588448114693165</v>
       </c>
       <c r="EX5" t="n">
-        <v>3.562559140846133e-05</v>
+        <v>0.004763579927384853</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0002372161252424121</v>
+        <v>0.0492536723613739</v>
       </c>
       <c r="EZ5" t="n">
-        <v>6.738981028320268e-06</v>
+        <v>0.005513084586709738</v>
       </c>
       <c r="FA5" t="n">
-        <v>8.835396147333086e-05</v>
+        <v>0.006470063701272011</v>
       </c>
       <c r="FB5" t="n">
-        <v>3.792001007241197e-05</v>
+        <v>0.006607901304960251</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0001474206219427288</v>
+        <v>0.03081711381673813</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0001142442488344386</v>
+        <v>0.0148435365408659</v>
       </c>
       <c r="FE5" t="n">
-        <v>1.67081416293513e-05</v>
+        <v>0.008988237008452415</v>
       </c>
       <c r="FF5" t="n">
-        <v>9.485553164267913e-06</v>
+        <v>0.001116602565161884</v>
       </c>
       <c r="FG5" t="n">
-        <v>5.282268466544338e-05</v>
+        <v>0.001257904805243015</v>
       </c>
       <c r="FH5" t="n">
-        <v>2.309653609700035e-05</v>
+        <v>0.03563015535473824</v>
       </c>
       <c r="FI5" t="n">
-        <v>9.304241393692791e-05</v>
+        <v>0.01970376446843147</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0002458585368003696</v>
+        <v>0.01220694370567799</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0001415561564499512</v>
+        <v>0.006082256324589252</v>
       </c>
       <c r="FL5" t="n">
-        <v>6.767958439013455e-06</v>
+        <v>0.04990570992231369</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0002505766460672021</v>
+        <v>0.0233989953994751</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001018349576042965</v>
+        <v>0.04793491587042809</v>
       </c>
       <c r="FO5" t="n">
-        <v>4.34348767157644e-05</v>
+        <v>0.04132162034511566</v>
       </c>
       <c r="FP5" t="n">
-        <v>8.820655784802511e-05</v>
+        <v>0.01197062153369188</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0006207945989444852</v>
+        <v>0.05434702336788177</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0001460673956898972</v>
+        <v>0.01987357437610626</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0002868794836103916</v>
+        <v>0.02790321782231331</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0002912297495640814</v>
+        <v>0.01189521048218012</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001616070512682199</v>
+        <v>0.04308517277240753</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0005050147301517427</v>
+        <v>0.007033523172140121</v>
       </c>
       <c r="FW5" t="n">
-        <v>5.536017852136865e-05</v>
+        <v>0.06324745714664459</v>
       </c>
       <c r="FX5" t="n">
-        <v>6.763025157852098e-05</v>
+        <v>0.02834958955645561</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0001351693354081362</v>
+        <v>0.02023359388113022</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0001638392714085057</v>
+        <v>0.007570438552647829</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0002990422945003957</v>
+        <v>0.03053929097950459</v>
       </c>
       <c r="GB5" t="n">
-        <v>5.283841892378405e-05</v>
+        <v>0.004336367826908827</v>
       </c>
       <c r="GC5" t="n">
-        <v>2.932919960585423e-05</v>
+        <v>0.0467514768242836</v>
       </c>
       <c r="GD5" t="n">
-        <v>3.87108520953916e-05</v>
+        <v>0.03412116691470146</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0001059228161466308</v>
+        <v>0.01344279665499926</v>
       </c>
       <c r="GF5" t="n">
-        <v>6.570570985786617e-05</v>
+        <v>0.0007131006568670273</v>
       </c>
       <c r="GG5" t="n">
-        <v>3.589993139030412e-05</v>
+        <v>0.01598687469959259</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0009190458804368973</v>
+        <v>0.4640321731567383</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03380119055509567</v>
+        <v>0.6075611114501953</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002701015677303076</v>
+        <v>0.03803973272442818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01650053262710571</v>
+        <v>0.06170940771698952</v>
       </c>
       <c r="E6" t="n">
-        <v>0.006508530117571354</v>
+        <v>0.003699779510498047</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03485697507858276</v>
+        <v>0.5574271678924561</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002559166867285967</v>
+        <v>0.09580979496240616</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01257401145994663</v>
+        <v>0.2963702082633972</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001774457050487399</v>
+        <v>0.1070341616868973</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005121848080307245</v>
+        <v>0.4503913521766663</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0312433447688818</v>
+        <v>0.7496124505996704</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001339048845693469</v>
+        <v>0.06957469135522842</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01641712337732315</v>
+        <v>0.06825511902570724</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002539339940994978</v>
+        <v>0.2193639874458313</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03313067182898521</v>
+        <v>0.5739989280700684</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0045106066390872</v>
+        <v>0.1362124383449554</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.004810147918760777</v>
+        <v>0.1357904970645905</v>
       </c>
       <c r="R6" t="n">
-        <v>0.001094372943043709</v>
+        <v>0.2530498206615448</v>
       </c>
       <c r="S6" t="n">
-        <v>0.002883101813495159</v>
+        <v>0.02493598684668541</v>
       </c>
       <c r="T6" t="n">
-        <v>0.004482035525143147</v>
+        <v>0.09620718657970428</v>
       </c>
       <c r="U6" t="n">
-        <v>4.633376374840736e-05</v>
+        <v>0.1111492142081261</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00104567501693964</v>
+        <v>0.2142187058925629</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002451400214340538</v>
+        <v>0.1215559989213943</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0003685073752421886</v>
+        <v>0.1073741465806961</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.002293624449521303</v>
+        <v>0.02743871510028839</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.002231694059446454</v>
+        <v>0.2320722937583923</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0032808524556458</v>
+        <v>0.06894969195127487</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001057120971381664</v>
+        <v>0.1209335625171661</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.003142671193927526</v>
+        <v>0.1314588189125061</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.002489623380824924</v>
+        <v>0.07895563542842865</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.004886428359895945</v>
+        <v>0.2109548598527908</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001702590496279299</v>
+        <v>0.413089245557785</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.001234949799254537</v>
+        <v>0.165967658162117</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.001791309332475066</v>
+        <v>0.03491991385817528</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.002579959342256188</v>
+        <v>0.1825510859489441</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0003370870254002512</v>
+        <v>0.05105357617139816</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.001978387590497732</v>
+        <v>0.1456546038389206</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.006779844872653484</v>
+        <v>0.1966227889060974</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001279108109883964</v>
+        <v>0.1431946456432343</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0008254512213170528</v>
+        <v>0.147858202457428</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.002917506499215961</v>
+        <v>0.1046202257275581</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.004645831417292356</v>
+        <v>0.03985586017370224</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.002166986232623458</v>
+        <v>0.09295488893985748</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.001439025742001832</v>
+        <v>0.1465397626161575</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.00254484242759645</v>
+        <v>0.1521234214305878</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.005374545231461525</v>
+        <v>0.3028199970722198</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.02521516196429729</v>
+        <v>0.5199538469314575</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.003092711558565497</v>
+        <v>0.0956084355711937</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.003984817303717136</v>
+        <v>0.03890932351350784</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.002662962768226862</v>
+        <v>0.2107668220996857</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.01459407340735197</v>
+        <v>0.2722114622592926</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.004912559874355793</v>
+        <v>0.01790324412286282</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.00256741140037775</v>
+        <v>0.01759144105017185</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.003450070973485708</v>
+        <v>0.1102058589458466</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.002878493862226605</v>
+        <v>0.04715131223201752</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.003920234739780426</v>
+        <v>0.072215735912323</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.008557816036045551</v>
+        <v>0.07186504453420639</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.002939089201390743</v>
+        <v>0.07118163257837296</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.01207178831100464</v>
+        <v>0.02222689986228943</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.01384462788701057</v>
+        <v>0.1506680846214294</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.004844075534492731</v>
+        <v>0.04009394720196724</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.002491137012839317</v>
+        <v>0.0719861313700676</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.001820994191803038</v>
+        <v>0.03296374902129173</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.000467991572804749</v>
+        <v>0.0248575247824192</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.00347450515255332</v>
+        <v>0.006483126431703568</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.00105121941305697</v>
+        <v>0.002789493417367339</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.004528972320258617</v>
+        <v>0.07088731974363327</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.004090416710823774</v>
+        <v>0.00338860135525465</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0004713069938588887</v>
+        <v>0.08134216070175171</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.003881482407450676</v>
+        <v>0.259054571390152</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0009400075650773942</v>
+        <v>0.1039145588874817</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.00110019906423986</v>
+        <v>0.1093179881572723</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.003751842305064201</v>
+        <v>0.1033366695046425</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01199730671942234</v>
+        <v>0.3597005605697632</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.001300387550145388</v>
+        <v>0.09147296100854874</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.004048223607242107</v>
+        <v>0.1486252546310425</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0006866013281978667</v>
+        <v>0.08491025865077972</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.006363236345350742</v>
+        <v>0.2833438813686371</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.001906621735543013</v>
+        <v>0.006379906088113785</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.003654589178040624</v>
+        <v>0.09231036901473999</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.002997239585965872</v>
+        <v>0.1154096499085426</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.0002537864784244448</v>
+        <v>0.07083117961883545</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.005824042949825525</v>
+        <v>0.206496387720108</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.002512172097340226</v>
+        <v>0.02681757882237434</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.003621159121394157</v>
+        <v>0.02287756279110909</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0005380000802688301</v>
+        <v>0.01638989895582199</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.005690823774784803</v>
+        <v>0.1774064302444458</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.003067632438614964</v>
+        <v>0.1204451620578766</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.001625520526431501</v>
+        <v>0.06387408077716827</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.001918122638016939</v>
+        <v>0.04720157384872437</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.004417275544255972</v>
+        <v>0.04494944214820862</v>
       </c>
       <c r="CN6" t="n">
-        <v>4.209921462461352e-05</v>
+        <v>0.3219752907752991</v>
       </c>
       <c r="CO6" t="n">
-        <v>7.73109495639801e-05</v>
+        <v>0.07136815041303635</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.003088440513238311</v>
+        <v>0.2281016111373901</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.002362705068662763</v>
+        <v>0.2100198119878769</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0009546834626235068</v>
+        <v>0.2092770487070084</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.004318505525588989</v>
+        <v>0.0277307890355587</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.007585923187434673</v>
+        <v>0.01387681812047958</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0006987765082158148</v>
+        <v>0.008744086138904095</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.0001901026407722384</v>
+        <v>0.04910016059875488</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.00454976549372077</v>
+        <v>0.1866407841444016</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.002241150243207812</v>
+        <v>0.03486823290586472</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.004735579714179039</v>
+        <v>0.01099207997322083</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0002523273578844965</v>
+        <v>0.004309215117245913</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006124353967607021</v>
+        <v>0.1698120534420013</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.002694525755941868</v>
+        <v>0.08646775782108307</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.002635432872921228</v>
+        <v>0.09810875356197357</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0006791696650907397</v>
+        <v>0.04431211948394775</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.001678805681876838</v>
+        <v>0.04877893254160881</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.005555516108870506</v>
+        <v>0.0726083368062973</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.0005056742229498923</v>
+        <v>0.1266651153564453</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.006932707037776709</v>
+        <v>0.05335459113121033</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.00626304280012846</v>
+        <v>0.3236058056354523</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.00322488253004849</v>
+        <v>0.01836397498846054</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.003974194172769785</v>
+        <v>0.002572216093540192</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.006620505359023809</v>
+        <v>0.06460390239953995</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.00415235199034214</v>
+        <v>0.06511694192886353</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0006578680477105081</v>
+        <v>0.04739860445261002</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001217173412442207</v>
+        <v>0.1427002251148224</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.001047942670993507</v>
+        <v>0.07084184885025024</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.005745633039623499</v>
+        <v>0.01784911379218102</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.001018722774460912</v>
+        <v>0.06555571407079697</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.004460471216589212</v>
+        <v>0.1883742213249207</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.003323371056467295</v>
+        <v>0.07172257453203201</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0005608617793768644</v>
+        <v>0.2777656614780426</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.002918053418397903</v>
+        <v>0.06377119570970535</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0006308912998065352</v>
+        <v>0.0996508002281189</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.002391907386481762</v>
+        <v>0.01947095617651939</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.003523747669532895</v>
+        <v>0.05247129872441292</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.003512030467391014</v>
+        <v>0.1264175176620483</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0007200394757091999</v>
+        <v>0.2155789434909821</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001035696361213923</v>
+        <v>0.2321675270795822</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.001023073680698872</v>
+        <v>0.03952407836914062</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.001666840631514788</v>
+        <v>0.04932377114892006</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.001434338861145079</v>
+        <v>0.09428549557924271</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.002751560416072607</v>
+        <v>0.07784071564674377</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.004574889317154884</v>
+        <v>0.01186197437345982</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.002224595751613379</v>
+        <v>0.09579462558031082</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0008624161710031331</v>
+        <v>0.2283911257982254</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0023800078779459</v>
+        <v>0.04549472406506538</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.005490037612617016</v>
+        <v>0.09718666970729828</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.003845480736345053</v>
+        <v>0.06674955785274506</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.000516673899255693</v>
+        <v>0.06245047599077225</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0004138027434237301</v>
+        <v>0.05730658769607544</v>
       </c>
       <c r="EO6" t="n">
-        <v>5.663151387125254e-05</v>
+        <v>0.05274365469813347</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.004160802811384201</v>
+        <v>0.07339838147163391</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.002000767970457673</v>
+        <v>0.04383999109268188</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.002469022758305073</v>
+        <v>0.02620762586593628</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.001312821637839079</v>
+        <v>0.03554302826523781</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.005386313423514366</v>
+        <v>0.1522192806005478</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.00192614458501339</v>
+        <v>0.02744566090404987</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.005626020487397909</v>
+        <v>0.06955453008413315</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.001111620804294944</v>
+        <v>0.1602602899074554</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.0007526416447944939</v>
+        <v>0.07146568596363068</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004797128029167652</v>
+        <v>0.2278551161289215</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.001117271720431745</v>
+        <v>0.01606826484203339</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.004035881720483303</v>
+        <v>0.01175016164779663</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0004736992123071104</v>
+        <v>0.01650277338922024</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.005401418078690767</v>
+        <v>0.1708961725234985</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.003631731495261192</v>
+        <v>0.1140744984149933</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.001462873187847435</v>
+        <v>0.1065901145339012</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.001797553384676576</v>
+        <v>0.002252875128760934</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.001071836333721876</v>
+        <v>0.006323381327092648</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0002562320150900632</v>
+        <v>0.2698003947734833</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.002991694957017899</v>
+        <v>0.1190686747431755</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.006485667079687119</v>
+        <v>0.03440715000033379</v>
       </c>
       <c r="FK6" t="n">
-        <v>1.241962308995426e-06</v>
+        <v>0.0991799384355545</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0004630170296877623</v>
+        <v>0.2219338715076447</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.002036439022049308</v>
+        <v>0.1004406288266182</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.001847815234214067</v>
+        <v>0.4351855516433716</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.001736393081955612</v>
+        <v>0.0204339437186718</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.001350864302366972</v>
+        <v>0.1665438413619995</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.01007712911814451</v>
+        <v>0.2036694139242172</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0007930771680548787</v>
+        <v>0.3551920652389526</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.006278350949287415</v>
+        <v>0.2955003380775452</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001315622357651591</v>
+        <v>0.002992060035467148</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.003865431295707822</v>
+        <v>0.2860827147960663</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.002563798800110817</v>
+        <v>0.1240380555391312</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.001514869974926114</v>
+        <v>0.0130542479455471</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0004767626523971558</v>
+        <v>0.01587046682834625</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.003845370840281248</v>
+        <v>0.09442882984876633</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.003135597100481391</v>
+        <v>0.09250977635383606</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0008136879187077284</v>
+        <v>0.07216037064790726</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.001820048899389803</v>
+        <v>0.1067329794168472</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.003027399070560932</v>
+        <v>0.1458117514848709</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.002269788412377238</v>
+        <v>0.09945820271968842</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.008734759874641895</v>
+        <v>0.007169358432292938</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001331084873527288</v>
+        <v>0.1929120123386383</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.000802357099018991</v>
+        <v>0.2313359826803207</v>
       </c>
     </row>
     <row r="7">
@@ -4413,571 +4413,571 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.001706086448393762</v>
+        <v>0.0008615009719505906</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05159669741988182</v>
+        <v>0.002385033527389169</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003815741511061788</v>
+        <v>1.134797639679164e-05</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0007394223939627409</v>
+        <v>0.000729275809135288</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0003351727791596204</v>
+        <v>0.0002483919961377978</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03957074508070946</v>
+        <v>0.000920626858714968</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004483873955905437</v>
+        <v>0.0002528559125494212</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01942944340407848</v>
+        <v>0.0006466502672992647</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01672435365617275</v>
+        <v>0.0001328740327153355</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007229003123939037</v>
+        <v>0.0004836073785554618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05370419099926949</v>
+        <v>0.002614633878692985</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0009681922383606434</v>
+        <v>3.933240077458322e-05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004716707859188318</v>
+        <v>0.001001193071715534</v>
       </c>
       <c r="N8" t="n">
-        <v>0.006125133018940687</v>
+        <v>0.0006824976298958063</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03452211618423462</v>
+        <v>0.001132604782469571</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01099721528589725</v>
+        <v>8.975043783721048e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.004208879545331001</v>
+        <v>0.0001337520952802151</v>
       </c>
       <c r="R8" t="n">
-        <v>0.008753293193876743</v>
+        <v>0.0007015569135546684</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0019227514276281</v>
+        <v>0.0001590583415236324</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0008918836247175932</v>
+        <v>9.519925515633076e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.009562328457832336</v>
+        <v>0.0001375245483359322</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002254740800708532</v>
+        <v>0.0003563213685993105</v>
       </c>
       <c r="W8" t="n">
-        <v>0.002645286032930017</v>
+        <v>0.0005006865831092</v>
       </c>
       <c r="X8" t="n">
-        <v>0.00708096195012331</v>
+        <v>0.0003621316864155233</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0009806696325540543</v>
+        <v>0.0003025929909199476</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.005963257048279047</v>
+        <v>0.0004443842626642436</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009865394094958901</v>
+        <v>5.525553569896147e-05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005930446088314056</v>
+        <v>0.0001579042582307011</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.005038633942604065</v>
+        <v>6.644996756222099e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.01289544254541397</v>
+        <v>0.0001989693264476955</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002664155326783657</v>
+        <v>0.0008004726842045784</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004603694658726454</v>
+        <v>0.001092045335099101</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.11883632093668e-05</v>
+        <v>0.0004270909412298352</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002707904204726219</v>
+        <v>0.0001062936935340986</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0003235200420022011</v>
+        <v>0.000674080743920058</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.001758819329552352</v>
+        <v>5.72195858694613e-06</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.008551626466214657</v>
+        <v>0.0002459287061356008</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.005445851944386959</v>
+        <v>0.0004734824178740382</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.01253698021173477</v>
+        <v>0.0002644764317665249</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002037270925939083</v>
+        <v>0.000378134980564937</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.006574473343789577</v>
+        <v>2.342829247936606e-06</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.004967096261680126</v>
+        <v>0.0002032388583756983</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003579337615519762</v>
+        <v>0.000412363006034866</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.006963875610381365</v>
+        <v>0.0002046658919425681</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.004853934515267611</v>
+        <v>7.895311136962846e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0008326402166858315</v>
+        <v>0.0004169294552411884</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03990281000733376</v>
+        <v>0.001812469679862261</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.01709840632975101</v>
+        <v>0.0003099899331573397</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003576493123546243</v>
+        <v>5.053421773482114e-06</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.01234375592321157</v>
+        <v>0.001040172995999455</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.006654478143900633</v>
+        <v>0.0006711734458804131</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.008719454519450665</v>
+        <v>3.283961268607527e-05</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.0006484277546405792</v>
+        <v>0.0002460023970343173</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0104760080575943</v>
+        <v>0.000281434622593224</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.006284214090555906</v>
+        <v>0.0002072092756861821</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01990831270813942</v>
+        <v>0.0004108473367523402</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.00630222400650382</v>
+        <v>0.0001947579439729452</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.007784836459904909</v>
+        <v>0.0004893459263257682</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0009797895327210426</v>
+        <v>0.0005273285205475986</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.02687260136008263</v>
+        <v>8.098446414805949e-05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.00126129062846303</v>
+        <v>4.638252721633762e-05</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.007498015649616718</v>
+        <v>0.0003188170376233757</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.005520678590983152</v>
+        <v>0.0001664534793235362</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.009008867666125298</v>
+        <v>5.244227213552222e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0005062590353190899</v>
+        <v>0.0001895138702820987</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.004339758306741714</v>
+        <v>4.81177048641257e-05</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.01096191816031933</v>
+        <v>2.425160346319899e-06</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.005530302412807941</v>
+        <v>0.0004481847281567752</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.002128840191289783</v>
+        <v>4.23064484493807e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.007765696849673986</v>
+        <v>0.0005972569924779236</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.004604165442287922</v>
+        <v>0.0002329357812413946</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0008719316101633012</v>
+        <v>0.0003884097095578909</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.00196397234685719</v>
+        <v>0.0002611496020108461</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.02048859000205994</v>
+        <v>0.001197586301714182</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.01296789292246103</v>
+        <v>0.0001567634753882885</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.002410748042166233</v>
+        <v>0.0001701060537016019</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.00942529458552599</v>
+        <v>0.0002029962779488415</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002436046954244375</v>
+        <v>0.0007210206240415573</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.002788517624139786</v>
+        <v>0.0003407267504371703</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0001770104863680899</v>
+        <v>7.693116640439257e-05</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.004576421342790127</v>
+        <v>0.0001523392566014081</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0014091229531914</v>
+        <v>0.000191763843758963</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.006564408075064421</v>
+        <v>0.0006970748654566705</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.004219610244035721</v>
+        <v>4.410655674291775e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0008688610978424549</v>
+        <v>0.0001853388966992497</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.00137578253634274</v>
+        <v>0.0001254391827387735</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.007855853997170925</v>
+        <v>0.0002888176531996578</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.003210018388926983</v>
+        <v>0.0001262616133317351</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00157287169713527</v>
+        <v>9.778125240700319e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002210782142356038</v>
+        <v>0.0001595535140950233</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.004131713882088661</v>
+        <v>0.0004734520043712109</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.01336886361241341</v>
+        <v>0.001012002001516521</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001326827681623399</v>
+        <v>0.0004660326812881976</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.007748844102025032</v>
+        <v>0.0004323011089581996</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.00731911463662982</v>
+        <v>6.082182517275214e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002114664996042848</v>
+        <v>0.000443747965618968</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.006420055404305458</v>
+        <v>0.0001131522876676172</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.01477071736007929</v>
+        <v>0.0001607676385901868</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.009855548851191998</v>
+        <v>0.0002044582215603441</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003777671372517943</v>
+        <v>9.008770575746894e-05</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.006856567692011595</v>
+        <v>0.0006435234099626541</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.00460390467196703</v>
+        <v>3.083498086198233e-05</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0005304553778842092</v>
+        <v>0.0001868826220743358</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.00189488974865526</v>
+        <v>0.0001440374471712857</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.008679811842739582</v>
+        <v>0.0003083908231928945</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.000922089908272028</v>
+        <v>5.167709332454251e-06</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001687070936895907</v>
+        <v>0.0002371484006289393</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.002955760108307004</v>
+        <v>0.000122489029308781</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0009856156539171934</v>
+        <v>0.0002883996930904686</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.006694110576063395</v>
+        <v>0.0002955097006633878</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.01078102551400661</v>
+        <v>0.0001606068108230829</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01061536837369204</v>
+        <v>0.0003451934899203479</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01496516913175583</v>
+        <v>0.0008428688743151724</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01491277944296598</v>
+        <v>4.4636195525527e-05</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.007730752229690552</v>
+        <v>0.0002532766666263342</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.002577697159722447</v>
+        <v>0.0001421871420461684</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.01169888395816088</v>
+        <v>6.096975994296372e-06</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.00435993168503046</v>
+        <v>0.0001498125493526459</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.00250877533107996</v>
+        <v>0.0004561659879982471</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.004182483069598675</v>
+        <v>0.0002028148737736046</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.001653262879699469</v>
+        <v>4.031331263831817e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0001064231619238853</v>
+        <v>0.000295978708891198</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.009469396434724331</v>
+        <v>0.0001932248414959759</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001214063260704279</v>
+        <v>0.0002092736831400543</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0007085166871547699</v>
+        <v>0.0004088093701284379</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.005771019030362368</v>
+        <v>0.0002094848896376789</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.001162315485998988</v>
+        <v>0.0003283753467258066</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.004511457402259111</v>
+        <v>0.000225734751438722</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.006352017633616924</v>
+        <v>0.000264172675088048</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.005359460599720478</v>
+        <v>0.0003729068266693503</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.004008767195045948</v>
+        <v>0.000160829906235449</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.006590310018509626</v>
+        <v>5.652225809171796e-06</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.002509568585082889</v>
+        <v>1.180831168312579e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.01312760263681412</v>
+        <v>0.0003337943053338677</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.009141584858298302</v>
+        <v>0.0002039076789515093</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0004357517464086413</v>
+        <v>5.274900468066335e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.009675119072198868</v>
+        <v>0.0001843181089498103</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.005309692118316889</v>
+        <v>0.0002748948172666132</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.004629302769899368</v>
+        <v>5.144511669641361e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004182782489806414</v>
+        <v>2.073934228974395e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.004410979803651571</v>
+        <v>0.0001453341101296246</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0003304863348603249</v>
+        <v>7.192573684733361e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.000240902416408062</v>
+        <v>0.0002074259682558477</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.001244829036295414</v>
+        <v>8.972328214440495e-05</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.002916628960520029</v>
+        <v>0.0002673268609214574</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.00404915539547801</v>
+        <v>0.0003554380382411182</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.00914638489484787</v>
+        <v>7.841813203413039e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.005583563353866339</v>
+        <v>1.905590761452913e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.008905374445021152</v>
+        <v>0.0002904667053371668</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.003756881225854158</v>
+        <v>0.0004469150444492698</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.006930057890713215</v>
+        <v>0.000159413815708831</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.009959077462553978</v>
+        <v>8.087469905149192e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.004996664356440306</v>
+        <v>0.0001924666721606627</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0009751291945576668</v>
+        <v>0.0001774562697391957</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.005377825815230608</v>
+        <v>0.0007705118041485548</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.005648575723171234</v>
+        <v>2.729791231104173e-05</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.003253428731113672</v>
+        <v>0.0002147095219697803</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.004499744158238173</v>
+        <v>6.767651939298958e-05</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.007179728709161282</v>
+        <v>0.0002509065670892596</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.001091100042685866</v>
+        <v>0.0001327997306361794</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0002434040361549705</v>
+        <v>0.0001574629714014009</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.003897178685292602</v>
+        <v>1.341141887678532e-05</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.001982571091502905</v>
+        <v>2.478839451214299e-05</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.004463204182684422</v>
+        <v>0.0004655745287891477</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.01135534513741732</v>
+        <v>0.0003246462438255548</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.004747764207422733</v>
+        <v>0.0002434029884170741</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.00125596672296524</v>
+        <v>3.103189374087378e-05</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.004893649369478226</v>
+        <v>0.0004966693231835961</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.006857265252619982</v>
+        <v>0.0002275861334055662</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.003704427741467953</v>
+        <v>0.000287233357084915</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.002578927902504802</v>
+        <v>0.0004693145165219903</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.004689935594797134</v>
+        <v>0.000536164385266602</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.01976138167083263</v>
+        <v>0.0008289487450383604</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.01349599659442902</v>
+        <v>0.0004653811920434237</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.007129980251193047</v>
+        <v>0.0005388662102632225</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.005098306573927402</v>
+        <v>0.0002682016929611564</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.003625939600169659</v>
+        <v>0.0005413158796727657</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.006923834793269634</v>
+        <v>0.0003424543829169124</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.01052712835371494</v>
+        <v>0.0001553257461637259</v>
       </c>
       <c r="FX8" t="n">
-        <v>8.539354894310236e-05</v>
+        <v>0.000122478959383443</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.01201437413692474</v>
+        <v>0.000290041120024398</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01044621970504522</v>
+        <v>9.119231253862381e-05</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.01028230600059032</v>
+        <v>0.0003438754938542843</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.008626613765954971</v>
+        <v>6.463107274612412e-05</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.01329541392624378</v>
+        <v>3.572538844309747e-06</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.004679946228861809</v>
+        <v>0.0004895960446447134</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.006154908798635006</v>
+        <v>0.0003613299923017621</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.003479107283055782</v>
+        <v>0.0002733925357460976</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.00411860179156065</v>
+        <v>0.0001551188761368394</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.04712750762701035</v>
+        <v>0.008006876334547997</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1433916836977005</v>
+        <v>0.01990574970841408</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02444591373205185</v>
+        <v>0.00539254117757082</v>
       </c>
       <c r="D10" t="n">
-        <v>0.07096441090106964</v>
+        <v>0.0006889058277010918</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1228159368038177</v>
+        <v>0.001079136505723</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2274920493364334</v>
+        <v>0.03465268388390541</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005219247192144394</v>
+        <v>0.008150866255164146</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1008017957210541</v>
+        <v>0.03821375966072083</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01917916536331177</v>
+        <v>0.002933923155069351</v>
       </c>
       <c r="J10" t="n">
-        <v>0.03184634819626808</v>
+        <v>0.007956402376294136</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1266021728515625</v>
+        <v>0.02234827354550362</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01622585579752922</v>
+        <v>0.006325609982013702</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04926870763301849</v>
+        <v>0.01363507658243179</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02824268862605095</v>
+        <v>0.00407213531434536</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1535261273384094</v>
+        <v>0.02387700974941254</v>
       </c>
       <c r="P10" t="n">
-        <v>0.002018595114350319</v>
+        <v>0.0006596932653337717</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1050875931978226</v>
+        <v>0.0496368445456028</v>
       </c>
       <c r="R10" t="n">
-        <v>0.01346465479582548</v>
+        <v>0.008851582184433937</v>
       </c>
       <c r="S10" t="n">
-        <v>0.002161890733987093</v>
+        <v>0.002583668567240238</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01089541334658861</v>
+        <v>0.004043509252369404</v>
       </c>
       <c r="U10" t="n">
-        <v>0.03008130937814713</v>
+        <v>0.001779689686372876</v>
       </c>
       <c r="V10" t="n">
-        <v>0.05383708328008652</v>
+        <v>0.004370162263512611</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05283989012241364</v>
+        <v>0.006392064969986677</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02362174354493618</v>
+        <v>0.0001890988642117009</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.02399009093642235</v>
+        <v>0.001981121953576803</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01517460215836763</v>
+        <v>0.006089956499636173</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01284207124263048</v>
+        <v>0.002381081227213144</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.008842597715556622</v>
+        <v>0.00208832835778594</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.009559900499880314</v>
+        <v>0.003197042969986796</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.01922261901199818</v>
+        <v>0.003899392439052463</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.007356845773756504</v>
+        <v>0.01952137053012848</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.01846639811992645</v>
+        <v>0.01512269303202629</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.03657849133014679</v>
+        <v>0.003605587175115943</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.04842814430594444</v>
+        <v>0.01289375871419907</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01701099425554276</v>
+        <v>0.005595390684902668</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.008317267522215843</v>
+        <v>0.005400441586971283</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0007229659240692854</v>
+        <v>0.002139980206266046</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02026758715510368</v>
+        <v>0.007401748560369015</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.01391260512173176</v>
+        <v>0.008498349227011204</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.01491841953247786</v>
+        <v>0.003427713178098202</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.01996278949081898</v>
+        <v>0.01280594058334827</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.04236643016338348</v>
+        <v>0.01889974810183048</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.007256674580276012</v>
+        <v>0.006864965427666903</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.03239411115646362</v>
+        <v>0.005420112051069736</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01266696862876415</v>
+        <v>0.003905531018972397</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.03142120689153671</v>
+        <v>0.002267573960125446</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.05692487955093384</v>
+        <v>0.05099945515394211</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.004505757242441177</v>
+        <v>0.004327575676143169</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.008752081543207169</v>
+        <v>0.005844161845743656</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1026384606957436</v>
+        <v>0.01618479005992413</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.1515335887670517</v>
+        <v>0.006645695772022009</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.003288226202130318</v>
+        <v>0.004082223400473595</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.04233349859714508</v>
+        <v>0.001854065572842956</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.02976066619157791</v>
+        <v>0.01582477800548077</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0002376860793447122</v>
+        <v>0.001583989826031029</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.04347167909145355</v>
+        <v>0.04059449583292007</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.01114590745419264</v>
+        <v>0.01018162071704865</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.05577361583709717</v>
+        <v>0.003896710695698857</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.06229211017489433</v>
+        <v>0.04113975539803505</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.02814295887947083</v>
+        <v>0.009958509355783463</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.01287032756954432</v>
+        <v>0.006155632436275482</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01184569858014584</v>
+        <v>0.004797149915248156</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.003300890326499939</v>
+        <v>0.001697693020105362</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.01239464804530144</v>
+        <v>0.003811085596680641</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.04050895571708679</v>
+        <v>0.003253988455981016</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.02219844609498978</v>
+        <v>0.01304663345217705</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.001404132228344679</v>
+        <v>0.002035704907029867</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.01987367495894432</v>
+        <v>0.004079055041074753</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.001059878151863813</v>
+        <v>0.006370036862790585</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.03378418833017349</v>
+        <v>0.0009386721067130566</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.03468512371182442</v>
+        <v>0.01319273002445698</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.02485044114291668</v>
+        <v>0.004165753722190857</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.02189884707331657</v>
+        <v>0.0004590784665197134</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.04884388670325279</v>
+        <v>0.02495099604129791</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.009585928171873093</v>
+        <v>0.0008802094962447882</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01435249019414186</v>
+        <v>0.007294859737157822</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.04464217275381088</v>
+        <v>0.00829159002751112</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.04976223409175873</v>
+        <v>0.0109811844304204</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.001387776806950569</v>
+        <v>0.006183596327900887</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.03857239708304405</v>
+        <v>0.004077326506376266</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.01572174206376076</v>
+        <v>0.001896071247756481</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.001120753353461623</v>
+        <v>0.000788174569606781</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0178097877651453</v>
+        <v>0.008609620854258537</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.005166313610970974</v>
+        <v>0.006525703705847263</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01972636207938194</v>
+        <v>0.001515828189440072</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01562050543725491</v>
+        <v>0.004114607349038124</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.03692580759525299</v>
+        <v>0.009901503100991249</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0004226444289088249</v>
+        <v>0.001747349160723388</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01262297574430704</v>
+        <v>0.009907422587275505</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.005211000330746174</v>
+        <v>0.002481870586052537</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.009126413613557816</v>
+        <v>0.005675360094755888</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02616786025464535</v>
+        <v>0.001320008770562708</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.001446793787181377</v>
+        <v>0.009806305170059204</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.01860999688506126</v>
+        <v>0.01736271008849144</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.07388193905353546</v>
+        <v>0.03708578273653984</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.01511320658028126</v>
+        <v>0.0009910929948091507</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.02197545021772385</v>
+        <v>0.0007283217273652554</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.01310364715754986</v>
+        <v>0.008049620315432549</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.03578456863760948</v>
+        <v>0.002745056757703424</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.003497880883514881</v>
+        <v>0.001315964153036475</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.01301814429461956</v>
+        <v>0.006442067679017782</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.007131898775696754</v>
+        <v>0.004870614036917686</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01916562579572201</v>
+        <v>0.0003942783805541694</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.02479862608015537</v>
+        <v>0.003403187496587634</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.04488848894834518</v>
+        <v>0.009819344617426395</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.004003733396530151</v>
+        <v>1.180707477033138e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.02583052776753902</v>
+        <v>0.00731393089517951</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0073570073582232</v>
+        <v>0.001347284996882081</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.01928194798529148</v>
+        <v>0.01090648118406534</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.08273906260728836</v>
+        <v>0.02594455704092979</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001155176549218595</v>
+        <v>0.007805121131241322</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.04370120167732239</v>
+        <v>0.01715913228690624</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1127617880702019</v>
+        <v>0.02365105226635933</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.06331970542669296</v>
+        <v>0.005966826342046261</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.027155676856637</v>
+        <v>0.007225709035992622</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.06460018455982208</v>
+        <v>0.003942491021007299</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.06895426660776138</v>
+        <v>0.02045224979519844</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.01473378483206034</v>
+        <v>0.00572125893086195</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.004172047600150108</v>
+        <v>0.001561424694955349</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.01600822433829308</v>
+        <v>0.002326939953491092</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.04472766444087029</v>
+        <v>0.004972299095243216</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001370499841868877</v>
+        <v>0.001658513792790473</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.005912914872169495</v>
+        <v>0.003067117650061846</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.01631993055343628</v>
+        <v>0.001641450799070299</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.04112929850816727</v>
+        <v>0.002020981628447771</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.001333547523245215</v>
+        <v>0.002649649046361446</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.01129958778619766</v>
+        <v>0.0009965819772332907</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.00741904228925705</v>
+        <v>0.006439663469791412</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01373250223696232</v>
+        <v>0.008860092610120773</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.005311834160238504</v>
+        <v>0.0120308781042695</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.05040508881211281</v>
+        <v>0.002166638150811195</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.02044681645929813</v>
+        <v>0.004158302210271358</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.008076312951743603</v>
+        <v>0.004964908119291067</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.03636591136455536</v>
+        <v>0.001597214723005891</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.03741450607776642</v>
+        <v>0.0170184001326561</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.01717322878539562</v>
+        <v>0.002467116573825479</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.009555777534842491</v>
+        <v>0.001051807310432196</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.01056214328855276</v>
+        <v>0.002244768664240837</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.002943611703813076</v>
+        <v>0.006977292709052563</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02868196740746498</v>
+        <v>0.009476199746131897</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0440874882042408</v>
+        <v>0.002126827836036682</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.005334111396223307</v>
+        <v>0.004434920381754637</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.01117003243416548</v>
+        <v>0.01266146637499332</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.006377573125064373</v>
+        <v>0.001335484208539128</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0009383077849633992</v>
+        <v>0.00229183561168611</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.001254206523299217</v>
+        <v>0.01161538250744343</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.01795785874128342</v>
+        <v>0.001276969909667969</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.007921215146780014</v>
+        <v>0.002997023286297917</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02109802514314651</v>
+        <v>0.007389340549707413</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.02723698876798153</v>
+        <v>0.01922289095818996</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001488802721723914</v>
+        <v>0.0103755434975028</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.04308160394430161</v>
+        <v>0.01232296973466873</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.007619599346071482</v>
+        <v>0.01306341961026192</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.002900394145399332</v>
+        <v>0.0001807848457247019</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.01259025000035763</v>
+        <v>0.009168716147542</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0133907338604331</v>
+        <v>0.005767804104834795</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.020231943577528</v>
+        <v>0.001145903719589114</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02366901561617851</v>
+        <v>0.002277592197060585</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04165038466453552</v>
+        <v>0.007776301354169846</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.003809747751802206</v>
+        <v>0.001055322587490082</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.02922459319233894</v>
+        <v>0.009119023568928242</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.001104767434298992</v>
+        <v>0.0002661769394762814</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.003907022997736931</v>
+        <v>0.003571425564587116</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.02489734068512917</v>
+        <v>0.01564574241638184</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.02619371749460697</v>
+        <v>0.001497183344326913</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.01445958111435175</v>
+        <v>0.006538128480315208</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01045199856162071</v>
+        <v>0.002329824026674032</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.02719314768910408</v>
+        <v>0.01168986968696117</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.003152217715978622</v>
+        <v>0.003455707337707281</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.01063660904765129</v>
+        <v>0.005649742670357227</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.016221659258008</v>
+        <v>0.002227406948804855</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.004151374101638794</v>
+        <v>0.0006815723609179258</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0004833381390199065</v>
+        <v>0.02922812476754189</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.01693501509726048</v>
+        <v>0.0507768988609314</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.02386743389070034</v>
+        <v>0.004892123863101006</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.08088171482086182</v>
+        <v>0.01187619939446449</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.04746229946613312</v>
+        <v>0.02408614009618759</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.03551556542515755</v>
+        <v>0.01158112846314907</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.03975903987884521</v>
+        <v>0.0009244857938028872</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.01202214229851961</v>
+        <v>0.03536368906497955</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.007173672318458557</v>
+        <v>0.009122783318161964</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.008135110139846802</v>
+        <v>0.007316973526030779</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.009591510519385338</v>
+        <v>0.0002605309709906578</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.008224392309784889</v>
+        <v>0.005483148619532585</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.1067797616124153</v>
+        <v>0.00466469768434763</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.01830577477812767</v>
+        <v>0.002900579944252968</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.02839246392250061</v>
+        <v>0.0001490967115387321</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.03268158435821533</v>
+        <v>0.0156968217343092</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0003768038004636765</v>
+        <v>0.007800483610481024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.806820364436135e-05</v>
+        <v>3.074165420002828e-07</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0001693118247203529</v>
+        <v>6.701253005303442e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>1.221925413119607e-05</v>
+        <v>2.429256710456684e-05</v>
       </c>
       <c r="D11" t="n">
-        <v>4.994038681616075e-05</v>
+        <v>7.707356417085975e-06</v>
       </c>
       <c r="E11" t="n">
-        <v>8.930711373977829e-06</v>
+        <v>1.95567754417425e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0001098079228540882</v>
+        <v>6.033369936631061e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>1.047545083565637e-05</v>
+        <v>1.041225232256693e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>5.804403917863965e-05</v>
+        <v>3.269231092417613e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>1.07554042187985e-05</v>
+        <v>5.682806659024209e-06</v>
       </c>
       <c r="J11" t="n">
-        <v>1.86575016414281e-05</v>
+        <v>2.947883331216872e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001454769808333367</v>
+        <v>8.565112511860207e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.691224724709173e-06</v>
+        <v>3.641854345914908e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>7.25085410522297e-05</v>
+        <v>2.385793050052598e-05</v>
       </c>
       <c r="N11" t="n">
-        <v>7.070140782161616e-06</v>
+        <v>1.423023968527559e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>9.620121272746474e-05</v>
+        <v>6.114384450484067e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>1.572034125274513e-05</v>
+        <v>2.887429445763701e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.192752046743408e-05</v>
+        <v>2.346433211641852e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.481976141803898e-06</v>
+        <v>6.979889349167934e-06</v>
       </c>
       <c r="S11" t="n">
-        <v>8.841059752739966e-06</v>
+        <v>9.607233550923411e-07</v>
       </c>
       <c r="T11" t="n">
-        <v>1.659597728576045e-05</v>
+        <v>8.679420716362074e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>9.9136627795815e-07</v>
+        <v>1.746007001202088e-06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.555540438857861e-05</v>
+        <v>1.007197170110885e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>2.597339516796637e-05</v>
+        <v>6.386580025719013e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>2.750174189714016e-06</v>
+        <v>2.380933619861025e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.992793952216743e-06</v>
+        <v>5.19868308401783e-06</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.794424502411857e-06</v>
+        <v>1.139991582022049e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.476679921732284e-08</v>
+        <v>1.323176320511266e-06</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78789377969224e-05</v>
+        <v>1.435632611901383e-06</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.848510484909639e-05</v>
+        <v>6.008214768371545e-06</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.191777573694708e-05</v>
+        <v>4.281071596778929e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.098612301575486e-05</v>
+        <v>1.42925709951669e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.064442130882526e-06</v>
+        <v>1.343856183666503e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.909644743136596e-05</v>
+        <v>1.53727232827805e-05</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.541346136946231e-06</v>
+        <v>2.877662154787686e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.392638816672843e-05</v>
+        <v>3.234759424231015e-05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.79165408553672e-06</v>
+        <v>8.963068466982804e-06</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.805432475521229e-05</v>
+        <v>3.667906185000902e-06</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.715200596663635e-05</v>
+        <v>1.707574483589269e-05</v>
       </c>
       <c r="AM11" t="n">
-        <v>7.97897155280225e-06</v>
+        <v>2.045497240033001e-06</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.679185051121749e-06</v>
+        <v>1.164820787380449e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>3.046562142117182e-06</v>
+        <v>2.964975237773615e-06</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.988306732731871e-05</v>
+        <v>8.26825726107927e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.059571513906121e-05</v>
+        <v>2.831254732882371e-07</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.831370173022151e-05</v>
+        <v>1.551243440189864e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.622392786288401e-06</v>
+        <v>8.03677539806813e-06</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.161426527891308e-05</v>
+        <v>1.029978011501953e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0001088858043658547</v>
+        <v>8.118545520119369e-05</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.717514330986887e-06</v>
+        <v>6.593621947104111e-06</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.471924017299898e-05</v>
+        <v>1.386935946356971e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.510789454390761e-05</v>
+        <v>2.927861169155221e-05</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.493198791053146e-05</v>
+        <v>4.750889274873771e-05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.300351505051367e-05</v>
+        <v>1.342334599030437e-06</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.674509232747369e-05</v>
+        <v>7.026053935987875e-06</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.403688879188849e-06</v>
+        <v>9.234731805918273e-06</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.110638762242161e-06</v>
+        <v>3.723709482983395e-07</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.528253339231014e-05</v>
+        <v>2.141284130630083e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.603153527365066e-05</v>
+        <v>1.801923281163909e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.27429536607815e-05</v>
+        <v>5.875339184058248e-07</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.168205487076193e-05</v>
+        <v>2.254260834888555e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.045056655537337e-05</v>
+        <v>1.942234462148917e-07</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.032680575008271e-05</v>
+        <v>1.145082114817342e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.613038307368697e-06</v>
+        <v>9.027580745168962e-06</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.391329174628481e-06</v>
+        <v>5.462269655254204e-06</v>
       </c>
       <c r="BL11" t="n">
-        <v>3.813095645455178e-06</v>
+        <v>4.227170848025708e-06</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.71274802798871e-05</v>
+        <v>6.880100954731461e-06</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.250794048246462e-05</v>
+        <v>4.886323040409479e-06</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.918081761687063e-05</v>
+        <v>3.134422968287254e-06</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.040508535283152e-06</v>
+        <v>3.60927060683025e-07</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.799924565508263e-06</v>
+        <v>4.1911807784345e-06</v>
       </c>
       <c r="BR11" t="n">
-        <v>1.410531422152417e-05</v>
+        <v>5.00826627103379e-06</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.506895932834595e-05</v>
+        <v>1.769942173268646e-06</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.732042609452037e-06</v>
+        <v>5.729382792196702e-06</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.685815732344054e-05</v>
+        <v>1.594060108800477e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.921976116951555e-05</v>
+        <v>4.159455784247257e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.959040653484408e-06</v>
+        <v>3.648727670224616e-06</v>
       </c>
       <c r="BX11" t="n">
-        <v>7.380849638138898e-07</v>
+        <v>1.331382554781158e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>7.2701218414295e-06</v>
+        <v>1.463762509956723e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.29420727211982e-05</v>
+        <v>3.577964889700525e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.872915840474889e-06</v>
+        <v>9.694030268292408e-06</v>
       </c>
       <c r="CB11" t="n">
-        <v>1.822592821554281e-05</v>
+        <v>8.463940503133927e-06</v>
       </c>
       <c r="CC11" t="n">
-        <v>8.743282705836464e-06</v>
+        <v>1.857786855907761e-06</v>
       </c>
       <c r="CD11" t="n">
-        <v>5.434347713162424e-06</v>
+        <v>4.803821411769604e-07</v>
       </c>
       <c r="CE11" t="n">
-        <v>2.8931004635524e-05</v>
+        <v>2.437574039504398e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.108704600483179e-05</v>
+        <v>4.837932465306949e-06</v>
       </c>
       <c r="CG11" t="n">
-        <v>1.479400816606358e-05</v>
+        <v>5.073679858469404e-06</v>
       </c>
       <c r="CH11" t="n">
-        <v>7.80857681093039e-06</v>
+        <v>4.20492369812564e-07</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.299812265642686e-05</v>
+        <v>1.309293202211848e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>8.777167749940418e-06</v>
+        <v>2.606718680908671e-07</v>
       </c>
       <c r="CK11" t="n">
-        <v>4.600231022777734e-06</v>
+        <v>6.117098109825747e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>4.14957230532309e-06</v>
+        <v>2.333557858946733e-06</v>
       </c>
       <c r="CM11" t="n">
-        <v>3.60658741556108e-05</v>
+        <v>4.755164809466805e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.769657658063807e-05</v>
+        <v>1.646815871936269e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>5.607672392216045e-06</v>
+        <v>1.602561678737402e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.506578337284736e-05</v>
+        <v>2.299960942764301e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>9.520420462649781e-06</v>
+        <v>2.395009141764604e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.445376528863562e-05</v>
+        <v>1.231142778124195e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>1.160560532298405e-05</v>
+        <v>6.170057531562634e-06</v>
       </c>
       <c r="CT11" t="n">
-        <v>1.698667074379046e-05</v>
+        <v>2.673733206393081e-06</v>
       </c>
       <c r="CU11" t="n">
-        <v>7.200950676633511e-06</v>
+        <v>5.885304290131899e-06</v>
       </c>
       <c r="CV11" t="n">
-        <v>4.885866474069189e-06</v>
+        <v>3.586422508305986e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.5099579943344e-05</v>
+        <v>2.166457852581516e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.442533903173171e-05</v>
+        <v>7.837095836293884e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.724344838294201e-05</v>
+        <v>8.768720363150351e-06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>7.083961918397108e-06</v>
+        <v>1.494396883572335e-06</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.447127579012886e-05</v>
+        <v>1.536589661554899e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>5.967526703898329e-06</v>
+        <v>2.130597522409516e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.099840119422879e-05</v>
+        <v>3.970322723034769e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.958624918392161e-06</v>
+        <v>1.694537559160381e-07</v>
       </c>
       <c r="DE11" t="n">
-        <v>1.536961826786865e-05</v>
+        <v>1.925957349158125e-06</v>
       </c>
       <c r="DF11" t="n">
-        <v>2.737868271651678e-05</v>
+        <v>1.50944761116989e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.480198574834503e-05</v>
+        <v>6.676993507426232e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>2.569638309068978e-05</v>
+        <v>6.450351975217927e-06</v>
       </c>
       <c r="DI11" t="n">
-        <v>2.131795190507546e-05</v>
+        <v>4.333982815296622e-06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>7.730853212706279e-06</v>
+        <v>2.465932630002499e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>2.167461025237571e-05</v>
+        <v>5.035110007156618e-06</v>
       </c>
       <c r="DL11" t="n">
-        <v>1.157355200120946e-05</v>
+        <v>2.868089177354705e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.143154233635869e-05</v>
+        <v>7.809741873643361e-06</v>
       </c>
       <c r="DN11" t="n">
-        <v>5.237295226834249e-06</v>
+        <v>6.305757324298611e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.8586604205193e-06</v>
+        <v>7.270863079611445e-06</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.764473255316261e-06</v>
+        <v>4.224270014674403e-06</v>
       </c>
       <c r="DQ11" t="n">
-        <v>1.141325446951669e-05</v>
+        <v>4.080372946191346e-06</v>
       </c>
       <c r="DR11" t="n">
-        <v>1.318760314461542e-05</v>
+        <v>1.370936047351279e-06</v>
       </c>
       <c r="DS11" t="n">
-        <v>5.886571670998819e-06</v>
+        <v>9.306910214945674e-06</v>
       </c>
       <c r="DT11" t="n">
-        <v>1.330299164692406e-05</v>
+        <v>6.453426976804622e-06</v>
       </c>
       <c r="DU11" t="n">
-        <v>9.043822501553223e-06</v>
+        <v>1.338730908173602e-05</v>
       </c>
       <c r="DV11" t="n">
-        <v>3.453689259913517e-06</v>
+        <v>3.888900209858548e-06</v>
       </c>
       <c r="DW11" t="n">
-        <v>8.791357686277479e-07</v>
+        <v>1.163929482572712e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>1.727053495415021e-05</v>
+        <v>1.356189841317246e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.273354978882708e-07</v>
+        <v>1.138484731200151e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>7.50426079321187e-06</v>
+        <v>7.81657945481129e-07</v>
       </c>
       <c r="EA11" t="n">
-        <v>4.963885658071376e-06</v>
+        <v>1.697421976132318e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.570045697008027e-06</v>
+        <v>1.494805565016577e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>8.055161742959172e-06</v>
+        <v>5.708491244149627e-06</v>
       </c>
       <c r="ED11" t="n">
-        <v>3.548357199179009e-06</v>
+        <v>1.443642941012513e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>5.318956937117036e-06</v>
+        <v>1.378651450067991e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>8.406094821111765e-06</v>
+        <v>4.256005922798067e-06</v>
       </c>
       <c r="EG11" t="n">
-        <v>2.140098149538971e-05</v>
+        <v>1.175962188426638e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>1.891264764708467e-05</v>
+        <v>2.737189333856804e-06</v>
       </c>
       <c r="EI11" t="n">
-        <v>1.221640741277952e-05</v>
+        <v>7.831827133486513e-07</v>
       </c>
       <c r="EJ11" t="n">
-        <v>3.177410690113902e-07</v>
+        <v>7.341606760746799e-06</v>
       </c>
       <c r="EK11" t="n">
-        <v>1.443004657630809e-05</v>
+        <v>4.318389983382076e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>1.088829776563216e-05</v>
+        <v>3.897717306244886e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>9.836202252699877e-07</v>
+        <v>5.659178441419499e-06</v>
       </c>
       <c r="EN11" t="n">
-        <v>1.952577122210641e-07</v>
+        <v>3.872323759424035e-07</v>
       </c>
       <c r="EO11" t="n">
-        <v>6.144972303445684e-06</v>
+        <v>7.955803994263988e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>1.99332043848699e-05</v>
+        <v>8.717912351130508e-06</v>
       </c>
       <c r="EQ11" t="n">
-        <v>7.493544217140879e-06</v>
+        <v>2.52282120527525e-06</v>
       </c>
       <c r="ER11" t="n">
-        <v>2.27049458771944e-05</v>
+        <v>1.165401226899121e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>8.389462891500443e-06</v>
+        <v>1.170693212770857e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>2.078644683933817e-06</v>
+        <v>5.607948878605384e-07</v>
       </c>
       <c r="EU11" t="n">
-        <v>1.076905573427211e-05</v>
+        <v>7.973227411639527e-07</v>
       </c>
       <c r="EV11" t="n">
-        <v>1.733173667162191e-05</v>
+        <v>5.175739715923555e-06</v>
       </c>
       <c r="EW11" t="n">
-        <v>5.018475349061191e-06</v>
+        <v>1.269725999009097e-05</v>
       </c>
       <c r="EX11" t="n">
-        <v>8.418084689765237e-06</v>
+        <v>1.308267201238777e-07</v>
       </c>
       <c r="EY11" t="n">
-        <v>2.439608942950144e-05</v>
+        <v>2.618878170324024e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>7.307601208594861e-06</v>
+        <v>5.782350399385905e-06</v>
       </c>
       <c r="FA11" t="n">
-        <v>1.524276194686536e-05</v>
+        <v>7.359865321632242e-06</v>
       </c>
       <c r="FB11" t="n">
-        <v>7.194532372523099e-06</v>
+        <v>1.32804416352883e-06</v>
       </c>
       <c r="FC11" t="n">
-        <v>1.38708928716369e-05</v>
+        <v>1.554525624669623e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>1.068201163434424e-05</v>
+        <v>1.072699888027273e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>5.278940989228431e-06</v>
+        <v>5.994529601593968e-06</v>
       </c>
       <c r="FF11" t="n">
-        <v>7.375995664915536e-06</v>
+        <v>1.915795564855216e-06</v>
       </c>
       <c r="FG11" t="n">
-        <v>4.141790668654721e-06</v>
+        <v>2.697937588891364e-06</v>
       </c>
       <c r="FH11" t="n">
-        <v>2.888103381337714e-06</v>
+        <v>1.736868580337614e-05</v>
       </c>
       <c r="FI11" t="n">
-        <v>1.72417003341252e-06</v>
+        <v>6.64112394588301e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>3.213664604118094e-05</v>
+        <v>8.391791197936982e-06</v>
       </c>
       <c r="FK11" t="n">
-        <v>5.473827968671685e-06</v>
+        <v>2.559713948357967e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>1.607970261829905e-05</v>
+        <v>1.067052198777674e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>5.827422683069017e-06</v>
+        <v>2.194973149016732e-06</v>
       </c>
       <c r="FN11" t="n">
-        <v>1.072105260391254e-05</v>
+        <v>2.200277958763763e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>7.558153811260127e-06</v>
+        <v>1.5581252228003e-05</v>
       </c>
       <c r="FP11" t="n">
-        <v>9.132190825766884e-06</v>
+        <v>3.855076556646964e-06</v>
       </c>
       <c r="FQ11" t="n">
-        <v>3.214669413864613e-05</v>
+        <v>1.628802783670835e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>1.259089276572922e-05</v>
+        <v>1.682248148426879e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>3.62493701686617e-05</v>
+        <v>1.513668848929228e-06</v>
       </c>
       <c r="FT11" t="n">
-        <v>7.191817985585658e-06</v>
+        <v>9.882701306196395e-07</v>
       </c>
       <c r="FU11" t="n">
-        <v>1.15235516204848e-05</v>
+        <v>1.159704515885096e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>5.009233063901775e-07</v>
+        <v>1.528939174022526e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>4.821712991542881e-06</v>
+        <v>1.546094608784188e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>8.5808887888561e-06</v>
+        <v>1.672374128247611e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>2.249158387712669e-05</v>
+        <v>6.837593900854699e-06</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.157637416326907e-05</v>
+        <v>2.344072299820255e-06</v>
       </c>
       <c r="GA11" t="n">
-        <v>7.0425849116873e-06</v>
+        <v>2.026801666943356e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>1.002962449092593e-06</v>
+        <v>6.428622327803168e-07</v>
       </c>
       <c r="GC11" t="n">
-        <v>2.15685158764245e-05</v>
+        <v>2.287203824380413e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>1.8210432244814e-05</v>
+        <v>1.331642761215335e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>5.146900366526097e-05</v>
+        <v>7.181743058026768e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>9.74598151515238e-06</v>
+        <v>4.699178134615067e-06</v>
       </c>
       <c r="GG11" t="n">
-        <v>8.690360118634999e-06</v>
+        <v>5.631813564832555e-06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.0002569261705502868</v>
+        <v>0.0138594526797533</v>
       </c>
       <c r="B12" t="n">
-        <v>0.006609692703932524</v>
+        <v>0.2014886438846588</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003868931089527905</v>
+        <v>0.07909369468688965</v>
       </c>
       <c r="D12" t="n">
-        <v>0.003458371385931969</v>
+        <v>0.0002681082114577293</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004219986032694578</v>
+        <v>0.0005350853316485882</v>
       </c>
       <c r="F12" t="n">
-        <v>0.002607082715258002</v>
+        <v>0.07447630167007446</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001064754789695144</v>
+        <v>0.01416070759296417</v>
       </c>
       <c r="H12" t="n">
-        <v>2.600416337372735e-05</v>
+        <v>0.005689173936843872</v>
       </c>
       <c r="I12" t="n">
-        <v>0.000711263797711581</v>
+        <v>0.08349337428808212</v>
       </c>
       <c r="J12" t="n">
-        <v>9.420950664207339e-05</v>
+        <v>0.01303920336067677</v>
       </c>
       <c r="K12" t="n">
-        <v>0.005549685098230839</v>
+        <v>0.2140951454639435</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0005834503099322319</v>
+        <v>0.07895903289318085</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0006709636654704809</v>
+        <v>0.04157803952693939</v>
       </c>
       <c r="N12" t="n">
-        <v>0.002668990520760417</v>
+        <v>0.01210263557732105</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001524658990092576</v>
+        <v>0.02499697171151638</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001884516561403871</v>
+        <v>0.01815436966717243</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.001169559196569026</v>
+        <v>0.02765398100018501</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0002350172726437449</v>
+        <v>0.06655699759721756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0001475644967285916</v>
+        <v>0.002321450039744377</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0003211298317182809</v>
+        <v>0.04593747481703758</v>
       </c>
       <c r="U12" t="n">
-        <v>4.093526513315737e-06</v>
+        <v>0.05840082839131355</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001111340476199985</v>
+        <v>0.00202979682944715</v>
       </c>
       <c r="W12" t="n">
-        <v>2.013956509472337e-05</v>
+        <v>0.003715452970936894</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0004561323439702392</v>
+        <v>0.0273488275706768</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0007679261034354568</v>
+        <v>0.002901520347222686</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0003369658952578902</v>
+        <v>0.001989480806514621</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0009691821760497987</v>
+        <v>0.04037776961922646</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.000181459472514689</v>
+        <v>0.03371293097734451</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.296618524473161e-05</v>
+        <v>0.03353464603424072</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0007585816783830523</v>
+        <v>0.00871149729937315</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.001529120723716915</v>
+        <v>0.06925316900014877</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0008340721833519638</v>
+        <v>0.06533744186162949</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0006832614308223128</v>
+        <v>0.02426774427294731</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.02159639634192e-06</v>
+        <v>0.01661238074302673</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.001134496182203293</v>
+        <v>0.003466781228780746</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0007633311324752867</v>
+        <v>0.04974757879972458</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0003023351600859314</v>
+        <v>0.00135065009817481</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.001164352521300316</v>
+        <v>0.04674823954701424</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0003742194676306099</v>
+        <v>0.02814589254558086</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.000205071090022102</v>
+        <v>0.02038963139057159</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.0001040686765918508</v>
+        <v>0.07753124088048935</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.0007963345851749182</v>
+        <v>0.02644410729408264</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0002224900235887617</v>
+        <v>0.0004375679418444633</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.0006336114602163434</v>
+        <v>0.003849063999950886</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.0005959105328656733</v>
+        <v>0.00172579544596374</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0009227620321325958</v>
+        <v>0.02483098953962326</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.00344483251683414</v>
+        <v>0.1606118083000183</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.589319673366845e-05</v>
+        <v>0.01992252841591835</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.003229051828384399</v>
+        <v>0.03585038334131241</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.002787889679893851</v>
+        <v>0.007301939651370049</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.0015931345988065</v>
+        <v>0.03256534785032272</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.001227445434778929</v>
+        <v>2.207758370786905e-05</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0005417055217549205</v>
+        <v>0.01798063516616821</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.001255253911949694</v>
+        <v>0.04229332879185677</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0006799602415412664</v>
+        <v>0.0368536114692688</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0009882657323032618</v>
+        <v>0.01922118104994297</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0007962660165503621</v>
+        <v>0.03769119083881378</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.0002827342832460999</v>
+        <v>0.02963830158114433</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.00229259766638279</v>
+        <v>0.04979421943426132</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0009093203698284924</v>
+        <v>0.04110165685415268</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0002017795341089368</v>
+        <v>0.01475228648632765</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.001354760606773198</v>
+        <v>0.0009099338203668594</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0006865714676678181</v>
+        <v>0.01493593025952578</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.0003023807075805962</v>
+        <v>0.001166595611721277</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.0005953463260084391</v>
+        <v>0.04481054842472076</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0005496347439475358</v>
+        <v>0.02580063790082932</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.0001803446793928742</v>
+        <v>0.04853731766343117</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.001652097445912659</v>
+        <v>0.01322063151746988</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.0004579156229738146</v>
+        <v>0.004433023277670145</v>
       </c>
       <c r="BR12" t="n">
-        <v>7.308961357921362e-05</v>
+        <v>0.006985055282711983</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.001087880460545421</v>
+        <v>0.02146378345787525</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0001271529035875574</v>
+        <v>0.02442597597837448</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.0008739802287891507</v>
+        <v>0.003559029428288341</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.002418086165562272</v>
+        <v>0.09057976305484772</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.0001677167892921716</v>
+        <v>0.01530543901026249</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.001197055680677295</v>
+        <v>0.007147811818867922</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.001256694085896015</v>
+        <v>0.001601226627826691</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.000308571383357048</v>
+        <v>0.05111919716000557</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0006697450298815966</v>
+        <v>0.004142869263887405</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.0001812439295463264</v>
+        <v>0.006820493377745152</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.0008847461431287229</v>
+        <v>0.04403504729270935</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.0001967746502486989</v>
+        <v>0.003217346500605345</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0006596976309083402</v>
+        <v>0.06637629121541977</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.0002986209001392126</v>
+        <v>0.04395469650626183</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.0007419812027364969</v>
+        <v>0.01128632947802544</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0002263757487526163</v>
+        <v>0.001767314970493317</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.0004389882378745824</v>
+        <v>0.008079937659204006</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.316500856773928e-05</v>
+        <v>0.00286820693872869</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.0002326960093341768</v>
+        <v>0.001413157675415277</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.0007037990726530552</v>
+        <v>0.01983702555298805</v>
       </c>
       <c r="CM12" t="n">
-        <v>3.513004776323214e-05</v>
+        <v>0.0005991659127175808</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0009739127708598971</v>
+        <v>0.05529408901929855</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.0002735346206463873</v>
+        <v>0.02968351915478706</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.001629626727662981</v>
+        <v>0.04532971978187561</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.0003141250344924629</v>
+        <v>0.05658679455518723</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.001412756624631584</v>
+        <v>0.05506854504346848</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.001880883355624974</v>
+        <v>0.003520323429256678</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0008602262823842466</v>
+        <v>0.004339233972132206</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.0002640191523823887</v>
+        <v>0.005422721151262522</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.959348446689546e-05</v>
+        <v>0.007662517484277487</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.0007867297972552478</v>
+        <v>0.06963285803794861</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0004174627247266471</v>
+        <v>0.04655224829912186</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.001008506747893989</v>
+        <v>0.01052348595112562</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0003973670827690512</v>
+        <v>0.005648818798363209</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.0007277937838807702</v>
+        <v>0.01683145016431808</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.0002362709783483297</v>
+        <v>7.501663640141487e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.0003325887955725193</v>
+        <v>0.008113904856145382</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.0005996170802973211</v>
+        <v>0.02950182929635048</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0002848543517757207</v>
+        <v>0.02236615121364594</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.001192907686345279</v>
+        <v>0.1071000248193741</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.0006877155392430723</v>
+        <v>0.0705520436167717</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.004482119344174862</v>
+        <v>0.03702381998300552</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.00311884842813015</v>
+        <v>0.03037147596478462</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.00019127553969156</v>
+        <v>0.02428424917161465</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.001670649275183678</v>
+        <v>0.002282176399603486</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.002291039098054171</v>
+        <v>0.01251260191202164</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0003591579152271152</v>
+        <v>0.04222122579813004</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.0008034365018829703</v>
+        <v>0.01632010564208031</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0006339155370369554</v>
+        <v>0.008099695667624474</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.001695057027973235</v>
+        <v>0.04011612385511398</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0004495966713875532</v>
+        <v>0.001539054326713085</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.0003095737774856389</v>
+        <v>0.01807860285043716</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0004400762263685465</v>
+        <v>0.03461968898773193</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.0003914905246347189</v>
+        <v>0.009328229352831841</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0005257531302049756</v>
+        <v>0.009027805179357529</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.000858072133269161</v>
+        <v>0.01799469627439976</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0003877375565934926</v>
+        <v>0.006303761154413223</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0002108268818119541</v>
+        <v>0.03085304424166679</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.001275389455258846</v>
+        <v>0.03209144622087479</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0007161450921557844</v>
+        <v>0.008028427138924599</v>
       </c>
       <c r="EA12" t="n">
-        <v>4.300443833926693e-05</v>
+        <v>0.0406082421541214</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.0004700307326857001</v>
+        <v>0.03251810371875763</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.0003089249366894364</v>
+        <v>0.005429547745734453</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0007509382558055222</v>
+        <v>0.01792843639850616</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.0005121993599459529</v>
+        <v>0.02364045940339565</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0006754892528988421</v>
+        <v>0.003469561226665974</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.0004915582248941064</v>
+        <v>0.07251377403736115</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0007284729508683085</v>
+        <v>0.02767040021717548</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.0001058279376593418</v>
+        <v>0.003728773444890976</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.001096469117328525</v>
+        <v>0.003590132808312774</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.0008667883812449872</v>
+        <v>0.01594351977109909</v>
       </c>
       <c r="EL12" t="n">
-        <v>6.838163244538009e-06</v>
+        <v>0.00641817320138216</v>
       </c>
       <c r="EM12" t="n">
-        <v>3.77084688807372e-05</v>
+        <v>0.006289047189056873</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0002441265678498894</v>
+        <v>0.02623404003679752</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0001380201574647799</v>
+        <v>0.0199746061116457</v>
       </c>
       <c r="EP12" t="n">
-        <v>5.678088928107172e-05</v>
+        <v>0.02468184940516949</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0004279576824046671</v>
+        <v>0.01356371305882931</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.0005158220883458853</v>
+        <v>0.0002859062515199184</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0002062892453977838</v>
+        <v>0.001298871356993914</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.001193783595226705</v>
+        <v>0.01048021484166384</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0005463977577164769</v>
+        <v>0.007032966241240501</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.0007331525557674468</v>
+        <v>0.00457991287112236</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0003036496927961707</v>
+        <v>0.008866236545145512</v>
       </c>
       <c r="EX12" t="n">
-        <v>9.617819159757346e-05</v>
+        <v>0.002411636523902416</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0007178717060014606</v>
+        <v>0.07064235955476761</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.0001502101367805153</v>
+        <v>0.04342649132013321</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0008447320433333516</v>
+        <v>0.01418593339622021</v>
       </c>
       <c r="FB12" t="n">
-        <v>4.647307650884613e-05</v>
+        <v>0.004287136252969503</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.0004555926716420799</v>
+        <v>0.01309425197541714</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0001777716825017706</v>
+        <v>0.001051270868629217</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0002149122592527419</v>
+        <v>0.002169866114854813</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.0007592440233565867</v>
+        <v>0.02701463177800179</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.0002091462374664843</v>
+        <v>0.009384467266499996</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.001049558748491108</v>
+        <v>0.05663962662220001</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.0001149099334725179</v>
+        <v>0.01331167295575142</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001130390679463744</v>
+        <v>0.03659824654459953</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.0007074701134115458</v>
+        <v>0.03335953503847122</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.0001406096271239221</v>
+        <v>0.008480740711092949</v>
       </c>
       <c r="FM12" t="n">
-        <v>2.023667911998928e-05</v>
+        <v>0.01090644672513008</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0008960529812611639</v>
+        <v>0.01610110327601433</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.000243592745391652</v>
+        <v>0.03906045854091644</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0001701656437944621</v>
+        <v>0.009365035220980644</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.001404424314387143</v>
+        <v>0.07382631301879883</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0001280395808862522</v>
+        <v>0.09652338922023773</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.001726935617625713</v>
+        <v>0.04047407582402229</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001429514726623893</v>
+        <v>0.006821898743510246</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.000501857022754848</v>
+        <v>0.02076570689678192</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.000469266640720889</v>
+        <v>0.007850689813494682</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0001706622715573758</v>
+        <v>0.03186572343111038</v>
       </c>
       <c r="FX12" t="n">
-        <v>4.445447120815516e-05</v>
+        <v>0.0143289677798748</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.0002707119565457106</v>
+        <v>0.06293994188308716</v>
       </c>
       <c r="FZ12" t="n">
-        <v>2.681260230019689e-05</v>
+        <v>0.08043094724416733</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.0002885188441723585</v>
+        <v>0.1105697900056839</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.001355539541691542</v>
+        <v>0.0007060831412672997</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.001523201819509268</v>
+        <v>0.01965549401938915</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0001835169969126582</v>
+        <v>0.009002561680972576</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.002024527406319976</v>
+        <v>0.01544036343693733</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.0003634050954133272</v>
+        <v>0.0280404519289732</v>
       </c>
       <c r="GG12" t="n">
-        <v>5.472945485962555e-05</v>
+        <v>0.02520805969834328</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.02023665234446526</v>
+        <v>7.534665201092139e-05</v>
       </c>
       <c r="B13" t="n">
-        <v>0.292483925819397</v>
+        <v>0.0005576666444540024</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00708004692569375</v>
+        <v>7.226043817354366e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1481190323829651</v>
+        <v>0.000266962219029665</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03883581608533859</v>
+        <v>0.0001723097084322944</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2278710603713989</v>
+        <v>0.0004957513883709908</v>
       </c>
       <c r="G13" t="n">
-        <v>0.009451810270547867</v>
+        <v>0.0002880532410927117</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1025386825203896</v>
+        <v>0.0004255693638697267</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01339906267821789</v>
+        <v>8.628311479697004e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05653790012001991</v>
+        <v>8.906482253223658e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2734870910644531</v>
+        <v>0.0006556103471666574</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005916742607951164</v>
+        <v>4.42415512225125e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1047808080911636</v>
+        <v>0.0004180268151685596</v>
       </c>
       <c r="N13" t="n">
-        <v>0.007402054499834776</v>
+        <v>0.0003941507020499557</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2180362641811371</v>
+        <v>0.0006857254775241017</v>
       </c>
       <c r="P13" t="n">
-        <v>0.009011683985590935</v>
+        <v>0.0002050140028586611</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.04233106225728989</v>
+        <v>0.000204438591026701</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008692416362464428</v>
+        <v>0.0001953012397279963</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01394344214349985</v>
+        <v>5.090924969408661e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0238085612654686</v>
+        <v>4.118708602618426e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02578062005341053</v>
+        <v>0.0001090407822630368</v>
       </c>
       <c r="V13" t="n">
-        <v>0.03893642872571945</v>
+        <v>7.305834151338786e-05</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06700211018323898</v>
+        <v>9.064349433174357e-05</v>
       </c>
       <c r="X13" t="n">
-        <v>0.02400580234825611</v>
+        <v>9.163391951005906e-05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.02178364619612694</v>
+        <v>6.288271833909675e-05</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.06639008969068527</v>
+        <v>0.0002684000646695495</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.04126325994729996</v>
+        <v>4.241197893861681e-05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.004982225596904755</v>
+        <v>0.000125059625133872</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.011800785548985</v>
+        <v>8.013929618755355e-05</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.007169472053647041</v>
+        <v>2.024113018705975e-05</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01238104980438948</v>
+        <v>0.0001714860554784536</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01525192707777023</v>
+        <v>0.0001393995771650225</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01654581539332867</v>
+        <v>0.0002202152245445177</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.01803364977240562</v>
+        <v>3.361756171216257e-06</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01741924695670605</v>
+        <v>0.0004604438436217606</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.01346874423325062</v>
+        <v>6.648371345363557e-05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02448061481118202</v>
+        <v>9.869087080005556e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.05435999855399132</v>
+        <v>5.532935756491497e-05</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.003185253590345383</v>
+        <v>0.0001239554403582588</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.009922495111823082</v>
+        <v>6.031141674611717e-05</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0008295127190649509</v>
+        <v>0.0001198409736389294</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.03444091230630875</v>
+        <v>8.363959204871207e-05</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.004564476665109396</v>
+        <v>3.791643030126579e-05</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01689633727073669</v>
+        <v>0.0002839821972884238</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.03104422055184841</v>
+        <v>5.179366780794226e-05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.04319792985916138</v>
+        <v>0.000186721736099571</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2123278677463531</v>
+        <v>0.0004530744336079806</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.007510749623179436</v>
+        <v>0.000103636208223179</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0579601563513279</v>
+        <v>0.0001846690138336271</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0213102400302887</v>
+        <v>0.0004541166126728058</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.119969367980957</v>
+        <v>0.0003557270392775536</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.03461265563964844</v>
+        <v>1.596295987837948e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.02722866088151932</v>
+        <v>0.0001033476728480309</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.07038221508264542</v>
+        <v>5.128590419190004e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.02555045858025551</v>
+        <v>2.467464582878165e-05</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04705157876014709</v>
+        <v>0.0002494638611096889</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.05751384049654007</v>
+        <v>4.750428342958912e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.001180743798613548</v>
+        <v>0.0002204653865192086</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.03977224603295326</v>
+        <v>0.0002713287831284106</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.06932011991739273</v>
+        <v>7.776821439620107e-05</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.02217846736311913</v>
+        <v>0.0001042695803334936</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0240033958107233</v>
+        <v>0.0003898584109265357</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01801223307847977</v>
+        <v>2.578301791800186e-05</v>
       </c>
       <c r="BL13" t="n">
-        <v>6.07944093644619e-05</v>
+        <v>1.744247674650978e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.05999037250876427</v>
+        <v>0.0001566176651977003</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.01013457030057907</v>
+        <v>1.257687290490139e-05</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.01626478508114815</v>
+        <v>6.100985410739668e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.004296740982681513</v>
+        <v>0.0001192022536997683</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0021707892883569</v>
+        <v>1.082958624465391e-05</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.02330923266708851</v>
+        <v>0.0003127656527794898</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.01446696370840073</v>
+        <v>0.0001382174814352766</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.01026926655322313</v>
+        <v>5.465006688609719e-05</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.01858248189091682</v>
+        <v>7.937208283692598e-05</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1120768263936043</v>
+        <v>0.0001838900498114526</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.02150421030819416</v>
+        <v>0.0001070218786480837</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.04431009665131569</v>
+        <v>0.0001270293432753533</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02744794078171253</v>
+        <v>0.0001438798062736169</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.05089700594544411</v>
+        <v>0.0001759260630933568</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01508958823978901</v>
+        <v>7.337889837799594e-05</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002004137262701988</v>
+        <v>9.08596848603338e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.04625633358955383</v>
+        <v>6.302618203335442e-06</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002628173679113388</v>
+        <v>1.800347308744676e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.04009556397795677</v>
+        <v>0.0001541579549666494</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.02793374285101891</v>
+        <v>6.107004992372822e-06</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0193618256598711</v>
+        <v>9.130638500209898e-05</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.008232364431023598</v>
+        <v>7.570914021926001e-05</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03524017333984375</v>
+        <v>0.0001640657865209505</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.02036489173769951</v>
+        <v>7.068131526466459e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.01557517237961292</v>
+        <v>1.986558891076129e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.02525391988456249</v>
+        <v>5.918956594541669e-05</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.06413847208023071</v>
+        <v>4.937113408232108e-05</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01272742636501789</v>
+        <v>0.0002526651951484382</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.00668724812567234</v>
+        <v>0.000278667634120211</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.05052947998046875</v>
+        <v>0.0003635098109953105</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.004549416713416576</v>
+        <v>1.18881871458143e-05</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.007799237035214901</v>
+        <v>0.0001584499841555953</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.05812123417854309</v>
+        <v>6.294358900049701e-05</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.05391817539930344</v>
+        <v>0.0001448770490242168</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01043883431702852</v>
+        <v>0.0001140822569141164</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0009416760876774788</v>
+        <v>4.393059134599753e-05</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.03571484610438347</v>
+        <v>0.0001403768837917596</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.02421785518527031</v>
+        <v>1.461784222556162e-07</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0353582426905632</v>
+        <v>0.0001221128040924668</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0107139041647315</v>
+        <v>5.167398194316775e-05</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.03668152168393135</v>
+        <v>0.0001857460592873394</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.02125009894371033</v>
+        <v>1.354455434920965e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.02972018532454967</v>
+        <v>6.652798219874967e-06</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.01393593475222588</v>
+        <v>2.273699283250608e-05</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.008743803948163986</v>
+        <v>6.404426676454023e-05</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.01422584056854248</v>
+        <v>6.493827095255256e-05</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.009145039133727551</v>
+        <v>0.0001894192537292838</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1083380952477455</v>
+        <v>6.811545608798042e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05626196786761284</v>
+        <v>0.0004130098968744278</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03664886578917503</v>
+        <v>0.0001364727795589715</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0003624125383794308</v>
+        <v>7.568365253973752e-05</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0464673638343811</v>
+        <v>0.0002460089162923396</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02717494778335094</v>
+        <v>0.0001168984599644318</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.004652342293411493</v>
+        <v>7.64687720220536e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.0008728886023163795</v>
+        <v>0.0001253829395864159</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.02266917936503887</v>
+        <v>8.17667823866941e-05</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.001039465889334679</v>
+        <v>9.521413448965177e-05</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.005997548811137676</v>
+        <v>1.343372059636749e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.008676251396536827</v>
+        <v>9.4499964689021e-06</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.002582381013780832</v>
+        <v>0.0001213371797348373</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.00330926850438118</v>
+        <v>0.0002812955062836409</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.02385660074651241</v>
+        <v>6.935997225809842e-05</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0007070107385516167</v>
+        <v>6.528028461616486e-05</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.03260188922286034</v>
+        <v>8.306747622555122e-05</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.02572822384536266</v>
+        <v>1.157809492724482e-06</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.01183806359767914</v>
+        <v>0.0002092532231472433</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.002768405247479677</v>
+        <v>0.0001907062687678263</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01771574653685093</v>
+        <v>8.62476445036009e-05</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.002267822623252869</v>
+        <v>1.691512443358079e-05</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.003897102084010839</v>
+        <v>8.392377640120685e-05</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.01626854762434959</v>
+        <v>0.0002663755149114877</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0177092682570219</v>
+        <v>7.179869044193765e-06</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.04576597362756729</v>
+        <v>3.84698978450615e-05</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01463432516902685</v>
+        <v>6.069092341931537e-05</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01107825711369514</v>
+        <v>1.854522997746244e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.003351270221173763</v>
+        <v>7.017249299678952e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.02215087972581387</v>
+        <v>0.0002036009827861562</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.02014325000345707</v>
+        <v>7.315113907679915e-05</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.008368423208594322</v>
+        <v>7.017305961198872e-06</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0127155464142561</v>
+        <v>3.504216874716803e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.0004197601228952408</v>
+        <v>4.79623704450205e-05</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.02099652588367462</v>
+        <v>8.23005975689739e-05</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.02553407661616802</v>
+        <v>0.0001343863550573587</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02960816398262978</v>
+        <v>0.0001055175744113512</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01975108310580254</v>
+        <v>4.633619755622931e-05</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.03215945512056351</v>
+        <v>0.0001414238213328645</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.05010540038347244</v>
+        <v>7.387626828858629e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.08045644313097</v>
+        <v>1.91890612768475e-05</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.008311638608574867</v>
+        <v>0.0001125578710343689</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.006566582713276148</v>
+        <v>4.816601358470507e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.03411320224404335</v>
+        <v>0.0002050547627732158</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01974849216639996</v>
+        <v>1.059525402524741e-06</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.02349472418427467</v>
+        <v>0.0001582198892720044</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.00770418718457222</v>
+        <v>4.600388274411671e-05</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03052231669425964</v>
+        <v>0.0001600273681106046</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.03587422892451286</v>
+        <v>5.3911058785161e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.02098602429032326</v>
+        <v>9.659115676186047e-07</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.02619985491037369</v>
+        <v>4.751405867864378e-06</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.01223727501928806</v>
+        <v>3.094939893344417e-05</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01259662676602602</v>
+        <v>0.0002150612272089347</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.02567204274237156</v>
+        <v>0.0001922720111906528</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.04128187149763107</v>
+        <v>8.973792137112468e-05</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.008640616200864315</v>
+        <v>0.0001440839696442708</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01895955577492714</v>
+        <v>0.0001054538297466934</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.002317844424396753</v>
+        <v>0.0001108450887841173</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.02321543544530869</v>
+        <v>0.0001574684429215267</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0205408725887537</v>
+        <v>0.0002202050527557731</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0225664246827364</v>
+        <v>0.0001202642306452617</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.04575827717781067</v>
+        <v>5.258404780761339e-05</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.03729543834924698</v>
+        <v>0.0003679635701701045</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01037292089313269</v>
+        <v>0.0001386669464409351</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.005012751556932926</v>
+        <v>0.0002657397708389908</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01237049698829651</v>
+        <v>5.152887024451047e-05</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.03562486916780472</v>
+        <v>2.819414658006281e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.006678466219455004</v>
+        <v>0.0001601911790203303</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01782098785042763</v>
+        <v>0.0001392734120599926</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.05956649035215378</v>
+        <v>2.178107752115466e-05</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01710194535553455</v>
+        <v>0.0002163868048228323</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.03143071383237839</v>
+        <v>0.0002044002321781591</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01636368595063686</v>
+        <v>4.077413905179128e-05</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01384407468140125</v>
+        <v>0.0002918321697507054</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.02384742721915245</v>
+        <v>0.0002643350453581661</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.1185244619846344</v>
+        <v>4.487401020014659e-05</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.002317036502063274</v>
+        <v>7.839269528631121e-05</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.009340224787592888</v>
+        <v>7.073197048157454e-05</v>
       </c>
     </row>
     <row r="14">
@@ -8965,571 +8965,571 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3.138248939649202e-05</v>
+        <v>7.554626790806651e-06</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0004674282972700894</v>
+        <v>0.0002754486631602049</v>
       </c>
       <c r="C16" t="n">
-        <v>1.84515356522752e-05</v>
+        <v>5.502663407241926e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>9.859175042947754e-05</v>
+        <v>0.0001462165964767337</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0001134976846515201</v>
+        <v>0.0001399179018335417</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0001523977553006262</v>
+        <v>0.0003619908238761127</v>
       </c>
       <c r="G16" t="n">
-        <v>7.015273877186701e-05</v>
+        <v>0.0001706143957562745</v>
       </c>
       <c r="H16" t="n">
-        <v>7.044524681987241e-05</v>
+        <v>0.0002385539701208472</v>
       </c>
       <c r="I16" t="n">
-        <v>8.509832696290687e-05</v>
+        <v>7.239920523716137e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>4.640034239855595e-05</v>
+        <v>2.291123564646114e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0004271079087629914</v>
+        <v>0.0003664773248601705</v>
       </c>
       <c r="L16" t="n">
-        <v>4.93716606797534e-06</v>
+        <v>4.237943721818738e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>6.537375884363428e-05</v>
+        <v>0.0002207380603067577</v>
       </c>
       <c r="N16" t="n">
-        <v>1.500888356531505e-05</v>
+        <v>0.0003150733537040651</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0001145301430369727</v>
+        <v>0.0004802141047548503</v>
       </c>
       <c r="P16" t="n">
-        <v>3.704111077240668e-05</v>
+        <v>0.0001079137000488117</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.368117566220462e-05</v>
+        <v>0.000112999026896432</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0001022789947455749</v>
+        <v>9.193950245389715e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>1.647205499466509e-05</v>
+        <v>2.754998422460631e-05</v>
       </c>
       <c r="T16" t="n">
-        <v>4.795105633093044e-05</v>
+        <v>1.290384534513578e-05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.106344825529959e-05</v>
+        <v>6.247054261621088e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>3.247761924285442e-05</v>
+        <v>2.748030055954587e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>5.132056685397401e-05</v>
+        <v>3.262343670940027e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>2.091487476718612e-05</v>
+        <v>5.846372368978336e-05</v>
       </c>
       <c r="Y16" t="n">
-        <v>9.27486689761281e-06</v>
+        <v>5.582731319009326e-05</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.26104442239739e-05</v>
+        <v>0.0001744499459164217</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.532338450895622e-05</v>
+        <v>2.412694630038459e-05</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.57317621819675e-05</v>
+        <v>3.89712986361701e-05</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.900178489857353e-05</v>
+        <v>1.308294667978771e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.492733645136468e-06</v>
+        <v>9.894029062706977e-06</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.117851545335725e-05</v>
+        <v>7.503878441639245e-05</v>
       </c>
       <c r="AF16" t="n">
-        <v>8.823926691547967e-06</v>
+        <v>0.0001311883970629424</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.130541113525396e-05</v>
+        <v>7.280467980308458e-05</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.289843658014433e-05</v>
+        <v>1.861169766925741e-05</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.258235624845838e-05</v>
+        <v>0.0002379000652581453</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.621904084458947e-05</v>
+        <v>2.509978367015719e-05</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.208008173620328e-05</v>
+        <v>2.176910129492171e-05</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.364281267044134e-05</v>
+        <v>1.569565938552842e-05</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.680937748460565e-05</v>
+        <v>1.532400347059593e-06</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.672427919809707e-05</v>
+        <v>2.400308403593954e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.540526449796744e-05</v>
+        <v>5.998814958729781e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.283255864516832e-05</v>
+        <v>5.790322393295355e-05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.189086419297382e-05</v>
+        <v>3.084833224420436e-05</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.655404376942897e-06</v>
+        <v>0.0001664635929046199</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.105169162154198e-05</v>
+        <v>3.282420038885903e-06</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.324645361630246e-06</v>
+        <v>5.925600999034941e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.000269425188889727</v>
+        <v>0.000348402390955016</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.745617479784414e-05</v>
+        <v>1.377148146275431e-05</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.099163612001576e-05</v>
+        <v>4.188874299870804e-05</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.813910603232216e-05</v>
+        <v>0.0001759891893016174</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.587333336938173e-05</v>
+        <v>0.0002788131241686642</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.000108918291516602</v>
+        <v>1.867568789748475e-05</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.516376818879507e-05</v>
+        <v>7.349184306804091e-05</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.094075484317727e-05</v>
+        <v>3.768634633161128e-05</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.504552973434329e-06</v>
+        <v>2.49532240559347e-06</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.125848009716719e-05</v>
+        <v>8.923991117626429e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.616265793330967e-05</v>
+        <v>2.859854430425912e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.388024222454987e-05</v>
+        <v>0.0001468786940677091</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.753930549370125e-05</v>
+        <v>9.086499630939215e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>6.391495844582096e-05</v>
+        <v>3.430104334256612e-05</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.285942198592238e-05</v>
+        <v>5.001942554372363e-05</v>
       </c>
       <c r="BJ16" t="n">
-        <v>4.329023795435205e-05</v>
+        <v>0.0001973840116988868</v>
       </c>
       <c r="BK16" t="n">
-        <v>8.994501695269719e-05</v>
+        <v>5.829126166645437e-05</v>
       </c>
       <c r="BL16" t="n">
-        <v>2.400615812803153e-05</v>
+        <v>8.061375410761684e-06</v>
       </c>
       <c r="BM16" t="n">
-        <v>5.321974094840698e-05</v>
+        <v>0.0001190886541735381</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.189045906357933e-05</v>
+        <v>5.150572178536095e-06</v>
       </c>
       <c r="BO16" t="n">
-        <v>2.611793570395093e-05</v>
+        <v>8.577387052355334e-05</v>
       </c>
       <c r="BP16" t="n">
-        <v>2.094975207000971e-05</v>
+        <v>8.214979607146233e-05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>2.528547156543937e-06</v>
+        <v>2.8553748052218e-05</v>
       </c>
       <c r="BR16" t="n">
-        <v>3.189599374309182e-05</v>
+        <v>0.0001332530373474583</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.262952749442775e-06</v>
+        <v>7.032876601442695e-05</v>
       </c>
       <c r="BT16" t="n">
-        <v>1.226696986122988e-05</v>
+        <v>6.742315599694848e-05</v>
       </c>
       <c r="BU16" t="n">
-        <v>8.889940545486752e-06</v>
+        <v>1.204423188028159e-05</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.0001623938733246177</v>
+        <v>0.0001661050628172234</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.979682929231785e-05</v>
+        <v>2.74775975412922e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>2.190635859733447e-05</v>
+        <v>8.158424316206947e-05</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.934121246449649e-05</v>
+        <v>4.699729470303282e-05</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.399740449414821e-05</v>
+        <v>0.0001262191362911835</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.388095734000672e-05</v>
+        <v>2.806710290315095e-05</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.434243237483315e-06</v>
+        <v>7.043380901450291e-05</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.665482886892278e-05</v>
+        <v>4.12250665249303e-06</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.151394801330753e-05</v>
+        <v>2.085928645101376e-05</v>
       </c>
       <c r="CE16" t="n">
-        <v>7.83202558523044e-05</v>
+        <v>6.928546645212919e-05</v>
       </c>
       <c r="CF16" t="n">
-        <v>1.510391120973509e-05</v>
+        <v>4.46761578132282e-06</v>
       </c>
       <c r="CG16" t="n">
-        <v>9.343822057417128e-06</v>
+        <v>6.235251203179359e-05</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.680721106822602e-05</v>
+        <v>4.705650280811824e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.100118333852151e-05</v>
+        <v>0.0001075120308087207</v>
       </c>
       <c r="CJ16" t="n">
-        <v>2.88691844616551e-05</v>
+        <v>4.456216265680268e-05</v>
       </c>
       <c r="CK16" t="n">
-        <v>8.916804290493019e-06</v>
+        <v>1.008114850264974e-05</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.067757304757833e-05</v>
+        <v>2.736132228164934e-05</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.0001113506004912779</v>
+        <v>4.308718416723423e-05</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.163501812901814e-05</v>
+        <v>0.000191124840057455</v>
       </c>
       <c r="CO16" t="n">
-        <v>2.510461490601301e-05</v>
+        <v>0.0001006840320769697</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0001419416221324354</v>
+        <v>0.0001900326169561595</v>
       </c>
       <c r="CQ16" t="n">
-        <v>6.459512951551005e-05</v>
+        <v>1.130203418142628e-05</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.0001039735288941301</v>
+        <v>0.000100678123999387</v>
       </c>
       <c r="CS16" t="n">
-        <v>7.676190580241382e-05</v>
+        <v>3.709238080773503e-05</v>
       </c>
       <c r="CT16" t="n">
-        <v>4.987229476682842e-05</v>
+        <v>5.919846080360003e-05</v>
       </c>
       <c r="CU16" t="n">
-        <v>4.830526086152531e-05</v>
+        <v>2.648674853844568e-05</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.927273842738941e-05</v>
+        <v>6.088473128329497e-06</v>
       </c>
       <c r="CW16" t="n">
-        <v>7.349321822402999e-05</v>
+        <v>6.437175034079701e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.358524241368286e-05</v>
+        <v>4.264413291821256e-06</v>
       </c>
       <c r="CY16" t="n">
-        <v>3.125383955193684e-05</v>
+        <v>8.054561476456001e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.281538218085188e-05</v>
+        <v>4.039100531372242e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>3.101386937487405e-06</v>
+        <v>0.0001276787661481649</v>
       </c>
       <c r="DB16" t="n">
-        <v>2.803410097840242e-05</v>
+        <v>9.229500392393675e-06</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.305348061781842e-05</v>
+        <v>8.725637599127367e-07</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.246443909825757e-05</v>
+        <v>1.56251153384801e-05</v>
       </c>
       <c r="DE16" t="n">
-        <v>3.806266977335326e-05</v>
+        <v>3.451423935985076e-06</v>
       </c>
       <c r="DF16" t="n">
-        <v>6.482492608483881e-05</v>
+        <v>0.0001622140989638865</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.800751462928019e-05</v>
+        <v>8.418591460213065e-05</v>
       </c>
       <c r="DH16" t="n">
-        <v>5.081366543890908e-05</v>
+        <v>1.822809099394362e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0001389850658597425</v>
+        <v>0.0001754132972564548</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.0001871412241598591</v>
+        <v>0.0001100195731851272</v>
       </c>
       <c r="DK16" t="n">
-        <v>2.279365071444772e-05</v>
+        <v>1.532948590465821e-05</v>
       </c>
       <c r="DL16" t="n">
-        <v>3.193409065715969e-05</v>
+        <v>8.922476990846917e-05</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.0001138390289270319</v>
+        <v>2.484361175447702e-05</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.644493179104757e-05</v>
+        <v>2.362649138376582e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.018881787080318e-05</v>
+        <v>3.662891685962677e-06</v>
       </c>
       <c r="DP16" t="n">
-        <v>4.188345337752253e-05</v>
+        <v>2.995444447151385e-05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>4.189364335616119e-05</v>
+        <v>3.965227006119676e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>2.828208198479842e-05</v>
+        <v>1.270416760235094e-06</v>
       </c>
       <c r="DS16" t="n">
-        <v>1.60346880875295e-05</v>
+        <v>2.244535153295146e-06</v>
       </c>
       <c r="DT16" t="n">
-        <v>7.034729060251266e-05</v>
+        <v>7.32435510144569e-05</v>
       </c>
       <c r="DU16" t="n">
-        <v>3.411257421248592e-05</v>
+        <v>0.0001454723824281245</v>
       </c>
       <c r="DV16" t="n">
-        <v>4.169124804320745e-05</v>
+        <v>3.20238177664578e-05</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.016414807963884e-05</v>
+        <v>2.696034243854228e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>6.174589361762628e-05</v>
+        <v>3.486333298496902e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>3.384593583177775e-06</v>
+        <v>9.33820592763368e-06</v>
       </c>
       <c r="DZ16" t="n">
-        <v>6.209306593518704e-05</v>
+        <v>0.0001294227840844542</v>
       </c>
       <c r="EA16" t="n">
-        <v>5.170873555471189e-05</v>
+        <v>7.662392454221845e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>2.430867971270345e-05</v>
+        <v>6.412101356545463e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.27323619381059e-05</v>
+        <v>7.897247996879742e-06</v>
       </c>
       <c r="ED16" t="n">
-        <v>4.549039294943213e-05</v>
+        <v>7.085907418513671e-05</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.0001002780991257168</v>
+        <v>0.0001471258292440325</v>
       </c>
       <c r="EF16" t="n">
-        <v>6.047507849871181e-05</v>
+        <v>2.351045986870304e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.0001104419061448425</v>
+        <v>2.378770295763388e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>6.423737886507297e-06</v>
+        <v>4.419573815539479e-05</v>
       </c>
       <c r="EI16" t="n">
-        <v>9.234645403921604e-08</v>
+        <v>1.505102409282699e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>5.315057023835834e-06</v>
+        <v>4.082029772689566e-05</v>
       </c>
       <c r="EK16" t="n">
-        <v>5.623965989798307e-05</v>
+        <v>0.0001148322044173256</v>
       </c>
       <c r="EL16" t="n">
-        <v>4.290399738238193e-05</v>
+        <v>5.689729732694104e-05</v>
       </c>
       <c r="EM16" t="n">
-        <v>2.263922215206549e-05</v>
+        <v>2.565561590017751e-05</v>
       </c>
       <c r="EN16" t="n">
-        <v>1.14161830424564e-05</v>
+        <v>6.913182915013749e-06</v>
       </c>
       <c r="EO16" t="n">
-        <v>2.445992868160829e-05</v>
+        <v>1.477954356232658e-06</v>
       </c>
       <c r="EP16" t="n">
-        <v>2.717870665946975e-05</v>
+        <v>8.180093573173508e-05</v>
       </c>
       <c r="EQ16" t="n">
-        <v>1.883559161797166e-05</v>
+        <v>5.738369509344921e-05</v>
       </c>
       <c r="ER16" t="n">
-        <v>4.53014399681706e-05</v>
+        <v>8.227476791944355e-05</v>
       </c>
       <c r="ES16" t="n">
-        <v>4.921059735352173e-05</v>
+        <v>1.98731850105105e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>8.794484529062174e-06</v>
+        <v>7.29490420781076e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>8.867942960932851e-05</v>
+        <v>4.072104638908058e-05</v>
       </c>
       <c r="EV16" t="n">
-        <v>6.772939377697185e-05</v>
+        <v>2.06279510166496e-05</v>
       </c>
       <c r="EW16" t="n">
-        <v>2.123968079104088e-05</v>
+        <v>5.794341996079311e-05</v>
       </c>
       <c r="EX16" t="n">
-        <v>2.517086613806896e-05</v>
+        <v>1.358070448986837e-06</v>
       </c>
       <c r="EY16" t="n">
-        <v>7.643481512786821e-05</v>
+        <v>0.0001034770830301568</v>
       </c>
       <c r="EZ16" t="n">
-        <v>8.976453500508796e-06</v>
+        <v>1.326303572568577e-05</v>
       </c>
       <c r="FA16" t="n">
-        <v>8.681041435920633e-06</v>
+        <v>9.245890396414325e-05</v>
       </c>
       <c r="FB16" t="n">
-        <v>1.219377736561e-05</v>
+        <v>3.167131944792345e-05</v>
       </c>
       <c r="FC16" t="n">
-        <v>4.172457920503803e-06</v>
+        <v>0.0001064886600943282</v>
       </c>
       <c r="FD16" t="n">
-        <v>4.493529195315205e-05</v>
+        <v>3.522800034261309e-05</v>
       </c>
       <c r="FE16" t="n">
-        <v>1.91099079529522e-05</v>
+        <v>2.761864834610606e-06</v>
       </c>
       <c r="FF16" t="n">
-        <v>3.675408515846357e-05</v>
+        <v>1.399952793690318e-06</v>
       </c>
       <c r="FG16" t="n">
-        <v>2.429770756862126e-05</v>
+        <v>7.806635039742105e-06</v>
       </c>
       <c r="FH16" t="n">
-        <v>2.262846101075411e-05</v>
+        <v>0.0001109946315409616</v>
       </c>
       <c r="FI16" t="n">
-        <v>2.687172309379093e-05</v>
+        <v>7.133724284358323e-05</v>
       </c>
       <c r="FJ16" t="n">
-        <v>6.81323726894334e-05</v>
+        <v>3.42834900948219e-05</v>
       </c>
       <c r="FK16" t="n">
-        <v>2.893361306632869e-05</v>
+        <v>9.000054706120864e-05</v>
       </c>
       <c r="FL16" t="n">
-        <v>1.242128928424791e-05</v>
+        <v>8.756159513723105e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>3.784141517826356e-05</v>
+        <v>8.29803102533333e-05</v>
       </c>
       <c r="FN16" t="n">
-        <v>1.553362562844995e-05</v>
+        <v>4.91024911752902e-05</v>
       </c>
       <c r="FO16" t="n">
-        <v>3.699460285133682e-05</v>
+        <v>0.0001022881624521688</v>
       </c>
       <c r="FP16" t="n">
-        <v>6.940004823263735e-05</v>
+        <v>1.408884418196976e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>2.840687193383928e-05</v>
+        <v>4.471472493605688e-06</v>
       </c>
       <c r="FR16" t="n">
-        <v>4.778662696480751e-05</v>
+        <v>0.0001684341405052692</v>
       </c>
       <c r="FS16" t="n">
-        <v>7.616729271830991e-05</v>
+        <v>9.002887236420065e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>1.764171611284837e-05</v>
+        <v>0.0002108096668962389</v>
       </c>
       <c r="FU16" t="n">
-        <v>6.488937651738524e-05</v>
+        <v>4.371036629891023e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>1.515650728833862e-05</v>
+        <v>3.06300753436517e-05</v>
       </c>
       <c r="FW16" t="n">
-        <v>9.527648217044771e-06</v>
+        <v>0.0001288376952288672</v>
       </c>
       <c r="FX16" t="n">
-        <v>2.617268728499766e-05</v>
+        <v>6.702392420265824e-05</v>
       </c>
       <c r="FY16" t="n">
-        <v>7.362080941675231e-05</v>
+        <v>5.621531454380602e-05</v>
       </c>
       <c r="FZ16" t="n">
-        <v>2.709897307795472e-05</v>
+        <v>9.877094998955727e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>1.115941995522007e-05</v>
+        <v>9.334144851891324e-05</v>
       </c>
       <c r="GB16" t="n">
-        <v>7.540901151514845e-06</v>
+        <v>1.525282459624577e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.209079346153885e-05</v>
+        <v>0.000173146981978789</v>
       </c>
       <c r="GD16" t="n">
-        <v>4.344449553173035e-05</v>
+        <v>0.000145695245009847</v>
       </c>
       <c r="GE16" t="n">
-        <v>9.199593478115276e-07</v>
+        <v>8.853967301547527e-07</v>
       </c>
       <c r="GF16" t="n">
-        <v>4.217899913783185e-05</v>
+        <v>8.099256956484169e-05</v>
       </c>
       <c r="GG16" t="n">
-        <v>2.132562076440081e-05</v>
+        <v>6.466444756370038e-05</v>
       </c>
     </row>
   </sheetData>
